--- a/Salidas/data_C_completa.xlsx
+++ b/Salidas/data_C_completa.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W101"/>
+  <dimension ref="A1:W100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="12" max="12" width="20.7109375" style="2" customWidth="1"/>
@@ -483,26 +483,26 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23851558</v>
+        <v>6729312</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ANTONIO AUGUSTO</t>
+          <t>ROSA JUANA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="J2">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2023-15</t>
+          <t>2018-32</t>
         </is>
       </c>
       <c r="L2" s="2">
-        <v>45239</v>
+        <v>43405</v>
       </c>
       <c r="M2" s="3">
-        <v>45026</v>
+        <v>43319</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -554,52 +554,52 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>22355486</v>
+        <v>93329075</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACERBI</t>
+          <t>SANCHEZ DELGADO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RAUL EDUARDO</t>
+          <t>BERTA PATRICIA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -624,34 +624,69 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1</t>
         </is>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="J3">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2025-44</t>
         </is>
       </c>
       <c r="L3" s="2">
-        <v>43627</v>
+        <v>46003</v>
       </c>
       <c r="M3" s="3">
-        <v>43493</v>
+        <v>45960</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tto en curso</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -662,16 +697,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>20897254</v>
+        <v>93060680</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MANSILLA</t>
+          <t>MIGUEZ OCHOA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SILVIA ALEJANDRA</t>
+          <t>SANDRA ROSSANA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -696,29 +731,29 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I4">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="J4">
         <v>2024</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2024-19</t>
+          <t>2024-45</t>
         </is>
       </c>
       <c r="L4" s="2">
-        <v>45139</v>
+        <v>45616</v>
       </c>
       <c r="M4" s="3">
-        <v>45420</v>
+        <v>45603</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -748,17 +783,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -769,21 +804,21 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>10691387</v>
+        <v>32822988</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MORUA</t>
+          <t>AGUERO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VICTOR HUGO</t>
+          <t>WALTER ALBERTO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -803,69 +838,34 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 3</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J5">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2025-27</t>
+          <t>2024-31</t>
         </is>
       </c>
       <c r="L5" s="2">
-        <v>45840</v>
+        <v>45506</v>
       </c>
       <c r="M5" s="3">
-        <v>45838</v>
+        <v>45503</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Tto en curso</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -876,16 +876,16 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>18613513</v>
+        <v>13985228</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GUENTELICAN</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JUAN ANDRES</t>
+          <t>ROBERTO ANDRES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -910,25 +910,25 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I6">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2025-33</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="L6" s="2">
-        <v>45883</v>
+        <v>44712</v>
       </c>
       <c r="M6" s="3">
-        <v>45883</v>
+        <v>44641</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -962,12 +962,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Tto en curso</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -983,16 +983,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>5123419</v>
+        <v>11227974</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ALBORNOZ</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JUANA EUSEBIA</t>
+          <t>ABEL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1017,99 +1017,64 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I7">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2024-22</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="L7" s="2">
-        <v>45498</v>
+        <v>44473</v>
       </c>
       <c r="M7" s="3">
-        <v>45440</v>
+        <v>44273</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>27112019</v>
+        <v>22503543</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>BESSE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SELVA BEATRIZ</t>
+          <t>PABLO JUAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1124,54 +1089,89 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>06. Caso DESCARTADO de Infección por VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="L8" s="2">
-        <v>45363</v>
+        <v>43496</v>
       </c>
       <c r="M8" s="3">
-        <v>45348</v>
+        <v>43475</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>24580401</v>
+        <v>18810111</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>BUSTAMANTE OYARZO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GRACIELA</t>
+          <t>SANDRA PAOLA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1196,29 +1196,29 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I9">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2023-25</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="L9" s="2">
-        <v>45119</v>
+        <v>44712</v>
       </c>
       <c r="M9" s="3">
-        <v>45098</v>
+        <v>44608</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1269,16 +1269,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>13744342</v>
+        <v>16013397</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>OLIVERO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>CLAUDIA MARCELA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1303,29 +1303,29 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 3</t>
+          <t>Virus Hepatitis C, genotipo 2</t>
         </is>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="J10">
         <v>2022</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-51</t>
         </is>
       </c>
       <c r="L10" s="2">
-        <v>44599</v>
+        <v>44972</v>
       </c>
       <c r="M10" s="3">
-        <v>44595</v>
+        <v>44916</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1376,21 +1376,21 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>32473179</v>
+        <v>17168769</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOBAR GUERRA</t>
+          <t>GERON</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CRISTIAN ARTURO</t>
+          <t>JUAN DOMINGO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1410,25 +1410,25 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="J11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2024-45</t>
         </is>
       </c>
       <c r="L11" s="2">
-        <v>45240</v>
+        <v>44655</v>
       </c>
       <c r="M11" s="3">
-        <v>44971</v>
+        <v>45601</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1483,16 +1483,16 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>31615481</v>
+        <v>27363443</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CANCINO</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SILVANA NATALIA</t>
+          <t>LUCAS CESAR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1517,69 +1517,34 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I12">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J12">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2023-15</t>
+          <t>2024-22</t>
         </is>
       </c>
       <c r="L12" s="2">
-        <v>45065</v>
+        <v>45440</v>
       </c>
       <c r="M12" s="3">
-        <v>45027</v>
+        <v>45439</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>LAGO PUELO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1590,16 +1555,16 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>13964678</v>
+        <v>20163816</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>RICARDI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JORGE DANIEL</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1619,30 +1584,30 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I13">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J13">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2020-14</t>
+          <t>2022-27</t>
         </is>
       </c>
       <c r="L13" s="2">
-        <v>44082</v>
+        <v>44971</v>
       </c>
       <c r="M13" s="3">
-        <v>43922</v>
+        <v>44746</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1651,7 +1616,42 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>HIV</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1662,26 +1662,26 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>27541551</v>
+        <v>10629822</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DURAN</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MARIA VANESA</t>
+          <t>OSVALDO MARIO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1696,69 +1696,34 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="J14">
         <v>2022</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-48</t>
         </is>
       </c>
       <c r="L14" s="2">
-        <v>44628</v>
+        <v>44923</v>
       </c>
       <c r="M14" s="3">
-        <v>44628</v>
+        <v>44894</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>RIO TERCERO</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1769,16 +1734,16 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>30566224</v>
+        <v>27207402</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>HUERTAS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SILVANA BEATRIZ</t>
+          <t>AMANDA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1803,69 +1768,34 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>05. Infección resuelta o falso anti VHC</t>
         </is>
       </c>
       <c r="I15">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="J15">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2024-21</t>
+          <t>2023-49</t>
         </is>
       </c>
       <c r="L15" s="2">
-        <v>45432</v>
+        <v>45265</v>
       </c>
       <c r="M15" s="3">
-        <v>45432</v>
+        <v>45265</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>HIV</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -1876,16 +1806,16 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>23079203</v>
+        <v>17460273</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SANTIAGO RUBEN</t>
+          <t>YOLANDA NOEMI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1895,7 +1825,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1910,25 +1840,25 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>07. En estudio para Hepatitis C</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I16">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J16">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2020-43</t>
+          <t>2023-47</t>
         </is>
       </c>
       <c r="L16" s="2">
-        <v>44154</v>
+        <v>45254</v>
       </c>
       <c r="M16" s="3">
-        <v>44124</v>
+        <v>45253</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1937,32 +1867,67 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>23611807</v>
+        <v>34113677</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAPOLEONE</t>
+          <t>ABALLAY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SILVANA JAQUELINA</t>
+          <t>PAMELA NOEMI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1982,69 +1947,34 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I17">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J17">
         <v>2023</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2023-43</t>
+          <t>2023-44</t>
         </is>
       </c>
       <c r="L17" s="2">
-        <v>45236</v>
+        <v>45240</v>
       </c>
       <c r="M17" s="3">
-        <v>45225</v>
+        <v>45230</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2055,21 +1985,21 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>16711304</v>
+        <v>39939562</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ACETO</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SANDRA ELISABET</t>
+          <t>MICAELA SILVIA VANESSA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2089,69 +2019,34 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 2</t>
+          <t>07. En estudio para Hepatitis C</t>
         </is>
       </c>
       <c r="I18">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J18">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2020-29</t>
+          <t>2021-47</t>
         </is>
       </c>
       <c r="L18" s="2">
-        <v>44178</v>
+        <v>44539</v>
       </c>
       <c r="M18" s="3">
-        <v>44025</v>
+        <v>44526</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2162,16 +2057,16 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>22213030</v>
+        <v>16051926</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>LOMBARDI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NESTOR DAVID</t>
+          <t>RAQUEL LILIANA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2181,7 +2076,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2196,25 +2091,25 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I19">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J19">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2019-46</t>
+          <t>2023-36</t>
         </is>
       </c>
       <c r="L19" s="2">
-        <v>43803</v>
+        <v>45183</v>
       </c>
       <c r="M19" s="3">
-        <v>43780</v>
+        <v>45177</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2223,42 +2118,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2269,26 +2129,26 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>38406872</v>
+        <v>23273835</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>REAL ADESSO</t>
+          <t>BARRETO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ANDREA BELEN</t>
+          <t>GUSTAVO ARIEL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2303,25 +2163,25 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I20">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J20">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2024-30</t>
         </is>
       </c>
       <c r="L20" s="2">
-        <v>44932</v>
+        <v>45565</v>
       </c>
       <c r="M20" s="3">
-        <v>44614</v>
+        <v>45498</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2330,32 +2190,32 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>5159683</v>
+        <v>13905203</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MARIA MIRTA</t>
+          <t>MARTA VIVIANA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2375,29 +2235,29 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I21">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J21">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2022-18</t>
+          <t>2024-31</t>
         </is>
       </c>
       <c r="L21" s="2">
-        <v>44712</v>
+        <v>45532</v>
       </c>
       <c r="M21" s="3">
-        <v>44686</v>
+        <v>45502</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2448,21 +2308,21 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>94509088</v>
+        <v>25319717</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YECGUANCHUY CHAVEZ</t>
+          <t>OROPEL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RAUL ANTONY</t>
+          <t>HIPOLITO LUJAN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2482,29 +2342,29 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I22">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>2023</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2023-16</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="L22" s="2">
-        <v>45246</v>
+        <v>44628</v>
       </c>
       <c r="M22" s="3">
-        <v>45034</v>
+        <v>44995</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2514,7 +2374,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2539,12 +2399,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -2555,21 +2415,21 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>12000042</v>
+        <v>22667988</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BUSTOS</t>
+          <t>ABAGNALE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ERNESTO REYES</t>
+          <t>SERGIO GABRIEL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2589,69 +2449,34 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I23">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="J23">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2021-34</t>
         </is>
       </c>
       <c r="L23" s="2">
-        <v>45712</v>
+        <v>44473</v>
       </c>
       <c r="M23" s="3">
-        <v>45705</v>
+        <v>44434</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -2662,26 +2487,26 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>13986860</v>
+        <v>35985565</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OSCAR JOSE</t>
+          <t>DAIANA BEATRIZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2696,25 +2521,25 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 4</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I24">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J24">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-24</t>
         </is>
       </c>
       <c r="L24" s="2">
-        <v>45498</v>
+        <v>45121</v>
       </c>
       <c r="M24" s="3">
-        <v>45348</v>
+        <v>45092</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2723,62 +2548,27 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
           <t>SIN DATOS</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>27817021</v>
+        <v>28060140</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>SEQUEIRA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ADRIANA MARISA</t>
+          <t>NANCY ELIZABETH</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2803,29 +2593,29 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I25">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J25">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2023-21</t>
+          <t>2019-34</t>
         </is>
       </c>
       <c r="L25" s="2">
-        <v>45240</v>
+        <v>43703</v>
       </c>
       <c r="M25" s="3">
-        <v>45068</v>
+        <v>43700</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2876,16 +2666,16 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>14857249</v>
+        <v>22803266</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ZALAZAR</t>
+          <t>MARTINENGO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO</t>
+          <t>PABLO DIEGO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2910,29 +2700,29 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 3</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I26">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="J26">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2019-47</t>
         </is>
       </c>
       <c r="L26" s="2">
-        <v>45707</v>
+        <v>43790</v>
       </c>
       <c r="M26" s="3">
-        <v>45707</v>
+        <v>43789</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2942,7 +2732,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2983,21 +2773,21 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>93329075</v>
+        <v>32733859</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SANCHEZ DELGADO</t>
+          <t>ACUÑA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BERTA PATRICIA</t>
+          <t>GRISELDA YSABEL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3017,25 +2807,25 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1</t>
+          <t>05. Infección resuelta o falso anti VHC</t>
         </is>
       </c>
       <c r="I27">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="J27">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2025-44</t>
+          <t>2023-15</t>
         </is>
       </c>
       <c r="L27" s="2">
-        <v>46003</v>
+        <v>45063</v>
       </c>
       <c r="M27" s="3">
-        <v>45960</v>
+        <v>45026</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3044,42 +2834,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Tto en curso</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3090,16 +2845,16 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>93060680</v>
+        <v>24820513</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MIGUEZ OCHOA</t>
+          <t>CRIADO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SANDRA ROSSANA</t>
+          <t>LORENA STELLA MARIS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3124,25 +2879,25 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I28">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J28">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2024-45</t>
+          <t>2021-52</t>
         </is>
       </c>
       <c r="L28" s="2">
-        <v>45616</v>
+        <v>44557</v>
       </c>
       <c r="M28" s="3">
-        <v>45603</v>
+        <v>44557</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3176,7 +2931,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3197,21 +2952,21 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>6729312</v>
+        <v>18853144</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VERA VIDAL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ROSA JUANA</t>
+          <t>LAURA ESTER</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3231,25 +2986,25 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I29">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J29">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2018-32</t>
+          <t>2024-18</t>
         </is>
       </c>
       <c r="L29" s="2">
-        <v>43405</v>
+        <v>45565</v>
       </c>
       <c r="M29" s="3">
-        <v>43319</v>
+        <v>45411</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3268,57 +3023,57 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>32822988</v>
+        <v>31931970</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AGUERO</t>
+          <t>DOS SANTOS TORRES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WALTER ALBERTO</t>
+          <t>LEONARDO DAMIAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3333,30 +3088,30 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
       <c r="I30">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="J30">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2024-31</t>
+          <t>2019-47</t>
         </is>
       </c>
       <c r="L30" s="2">
-        <v>45506</v>
+        <v>43851</v>
       </c>
       <c r="M30" s="3">
-        <v>45503</v>
+        <v>43791</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -3376,16 +3131,16 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>13985228</v>
+        <v>23079203</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ROBERTO ANDRES</t>
+          <t>SANTIAGO RUBEN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3410,69 +3165,34 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>06. Caso DESCARTADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I31">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="J31">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2020-43</t>
         </is>
       </c>
       <c r="L31" s="2">
-        <v>44712</v>
+        <v>44154</v>
       </c>
       <c r="M31" s="3">
-        <v>44641</v>
+        <v>44124</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -3483,26 +3203,26 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>11227974</v>
+        <v>95120818</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>MARTINEZ DIAZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ABEL</t>
+          <t>RAQUEL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3521,25 +3241,25 @@
         </is>
       </c>
       <c r="I32">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="J32">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2019-43</t>
         </is>
       </c>
       <c r="L32" s="2">
-        <v>44473</v>
+        <v>43864</v>
       </c>
       <c r="M32" s="3">
-        <v>44273</v>
+        <v>43761</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3555,16 +3275,16 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>22503543</v>
+        <v>21352851</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BESSE</t>
+          <t>RUIZ VARGAS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PABLO JUAN</t>
+          <t>CARLOS RAIMUNDO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3593,25 +3313,25 @@
         </is>
       </c>
       <c r="I33">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="J33">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2022-26</t>
         </is>
       </c>
       <c r="L33" s="2">
-        <v>43496</v>
+        <v>44182</v>
       </c>
       <c r="M33" s="3">
-        <v>43475</v>
+        <v>44743</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3641,7 +3361,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3651,7 +3371,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -3662,16 +3382,16 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>17168769</v>
+        <v>24846310</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GERON</t>
+          <t>SANDEZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JUAN DOMINGO</t>
+          <t>GRISELDA LILIANA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3681,7 +3401,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3696,25 +3416,25 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I34">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J34">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2024-45</t>
+          <t>2023-39</t>
         </is>
       </c>
       <c r="L34" s="2">
-        <v>44655</v>
+        <v>45246</v>
       </c>
       <c r="M34" s="3">
-        <v>45601</v>
+        <v>45196</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3723,42 +3443,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -3769,21 +3454,21 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>30339686</v>
+        <v>28010918</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>GAMARRA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VIVIANA ELISA</t>
+          <t>ALICIA ELISABET</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3807,21 +3492,21 @@
         </is>
       </c>
       <c r="I35">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J35">
         <v>2025</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2025-37</t>
+          <t>2025-45</t>
         </is>
       </c>
       <c r="L35" s="2">
-        <v>45910</v>
+        <v>45968</v>
       </c>
       <c r="M35" s="3">
-        <v>45910</v>
+        <v>45967</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3830,42 +3515,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -3876,26 +3526,26 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>16013397</v>
+        <v>33992074</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OLIVERO</t>
+          <t>LUNA ROMANO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLAUDIA MARCELA</t>
+          <t>MAXIMILIANO GASTON</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3910,69 +3560,34 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 2</t>
+          <t>07. En estudio para Hepatitis C</t>
         </is>
       </c>
       <c r="I36">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J36">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2022-51</t>
+          <t>2023-43</t>
         </is>
       </c>
       <c r="L36" s="2">
-        <v>44972</v>
+        <v>45275</v>
       </c>
       <c r="M36" s="3">
-        <v>44916</v>
+        <v>45225</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -3983,21 +3598,21 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>18810111</v>
+        <v>34375494</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BUSTAMANTE OYARZO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SANDRA PAOLA</t>
+          <t>GISELA BEATRIZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4012,74 +3627,39 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
       <c r="I37">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="J37">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2024-45</t>
         </is>
       </c>
       <c r="L37" s="2">
-        <v>44712</v>
+        <v>45617</v>
       </c>
       <c r="M37" s="3">
-        <v>44608</v>
+        <v>45604</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>HIV</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -4090,16 +3670,16 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>20163816</v>
+        <v>92828931</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RICARDI</t>
+          <t>CATELICAN CARDENAS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>MARIA OLINDA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4109,7 +3689,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4124,69 +3704,34 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I38">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J38">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2022-27</t>
+          <t>2020-21</t>
         </is>
       </c>
       <c r="L38" s="2">
-        <v>44971</v>
+        <v>43970</v>
       </c>
       <c r="M38" s="3">
-        <v>44746</v>
+        <v>43969</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>HIV</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -4197,21 +3742,21 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>27363443</v>
+        <v>22450956</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LUCAS CESAR</t>
+          <t>SERGIO WALTER</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4231,34 +3776,69 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I39">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J39">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2024-22</t>
+          <t>2025-29</t>
         </is>
       </c>
       <c r="L39" s="2">
-        <v>45440</v>
+        <v>45882</v>
       </c>
       <c r="M39" s="3">
-        <v>45439</v>
+        <v>45855</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>LAGO PUELO</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -4269,16 +3849,16 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>17460273</v>
+        <v>16666106</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YOLANDA NOEMI</t>
+          <t>SELVA NOEMI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4303,25 +3883,25 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I40">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="J40">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2023-47</t>
+          <t>2022-19</t>
         </is>
       </c>
       <c r="L40" s="2">
-        <v>45254</v>
+        <v>44705</v>
       </c>
       <c r="M40" s="3">
-        <v>45253</v>
+        <v>44694</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -4333,34 +3913,29 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4376,26 +3951,26 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>27207402</v>
+        <v>14225457</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HUERTAS</t>
+          <t>ARAOZ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AMANDA</t>
+          <t>ANGEL ANTONIO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4410,34 +3985,69 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>05. Infección resuelta o falso anti VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I41">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="J41">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2023-49</t>
+          <t>2022-16</t>
         </is>
       </c>
       <c r="L41" s="2">
-        <v>45265</v>
+        <v>44712</v>
       </c>
       <c r="M41" s="3">
-        <v>45265</v>
+        <v>44672</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -4448,26 +4058,26 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>10629822</v>
+        <v>12448939</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>CABALLERO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OSVALDO MARIO</t>
+          <t>GLORIA MABEL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4482,34 +4092,69 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 2</t>
         </is>
       </c>
       <c r="I42">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="J42">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2022-48</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="L42" s="2">
-        <v>44923</v>
+        <v>43468</v>
       </c>
       <c r="M42" s="3">
-        <v>44894</v>
+        <v>43468</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -4520,26 +4165,26 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>16051926</v>
+        <v>25369696</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LOMBARDI</t>
+          <t>MACIEL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RAQUEL LILIANA</t>
+          <t>CLAUDIO ABEL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4554,34 +4199,69 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I43">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J43">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2023-36</t>
+          <t>2018-26</t>
         </is>
       </c>
       <c r="L43" s="2">
-        <v>45183</v>
+        <v>43304</v>
       </c>
       <c r="M43" s="3">
-        <v>45177</v>
+        <v>43277</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -4592,26 +4272,26 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>39939562</v>
+        <v>93492923</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>SUA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MICAELA SILVIA VANESSA</t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4626,25 +4306,25 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>07. En estudio para Hepatitis C</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I44">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J44">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2021-47</t>
+          <t>2022-22</t>
         </is>
       </c>
       <c r="L44" s="2">
-        <v>44539</v>
+        <v>44711</v>
       </c>
       <c r="M44" s="3">
-        <v>44526</v>
+        <v>44711</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -4653,27 +4333,57 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>34113677</v>
+        <v>36733843</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ABALLAY</t>
+          <t>SANCHEZ GILARDI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PAMELA NOEMI</t>
+          <t>VERONICA SOLEDAD</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4693,39 +4403,39 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I45">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="J45">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2023-44</t>
+          <t>2020-38</t>
         </is>
       </c>
       <c r="L45" s="2">
-        <v>45240</v>
+        <v>44111</v>
       </c>
       <c r="M45" s="3">
-        <v>45230</v>
+        <v>44089</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -4736,16 +4446,16 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>13905203</v>
+        <v>900590791</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CHRUTOPHE MICHEL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MARTA VIVIANA</t>
+          <t>AUGUIN DARTHENAY</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4755,7 +4465,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4770,99 +4480,64 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I46">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="J46">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2024-31</t>
+          <t>2019-45</t>
         </is>
       </c>
       <c r="L46" s="2">
-        <v>45532</v>
+        <v>43775</v>
       </c>
       <c r="M46" s="3">
-        <v>45502</v>
+        <v>43773</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>sin dato</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>23273835</v>
+        <v>13335777</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>GUALTIERI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GUSTAVO ARIEL</t>
+          <t>SILVIA ESTELA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4881,25 +4556,25 @@
         </is>
       </c>
       <c r="I47">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J47">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2024-30</t>
+          <t>2019-50</t>
         </is>
       </c>
       <c r="L47" s="2">
-        <v>45565</v>
+        <v>43812</v>
       </c>
       <c r="M47" s="3">
-        <v>45498</v>
+        <v>43811</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4915,26 +4590,26 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>25319717</v>
+        <v>30339686</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OROPEL</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HIPOLITO LUJAN</t>
+          <t>VIVIANA ELISA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4949,29 +4624,29 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I48">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="J48">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-37</t>
         </is>
       </c>
       <c r="L48" s="2">
-        <v>44628</v>
+        <v>45910</v>
       </c>
       <c r="M48" s="3">
-        <v>44995</v>
+        <v>45910</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -5022,26 +4697,26 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>35985565</v>
+        <v>23627645</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>SPEHGT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DAIANA BEATRIZ</t>
+          <t>JORGE ENRIQUE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5056,34 +4731,69 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I49">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="J49">
         <v>2023</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2023-24</t>
+          <t>2023-43</t>
         </is>
       </c>
       <c r="L49" s="2">
-        <v>45121</v>
+        <v>45240</v>
       </c>
       <c r="M49" s="3">
-        <v>45092</v>
+        <v>45224</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -5094,16 +4804,16 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>22667988</v>
+        <v>23851558</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ABAGNALE</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SERGIO GABRIEL</t>
+          <t>ANTONIO AUGUSTO</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5128,34 +4838,69 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I50">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="J50">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2021-34</t>
+          <t>2023-15</t>
         </is>
       </c>
       <c r="L50" s="2">
-        <v>44473</v>
+        <v>45239</v>
       </c>
       <c r="M50" s="3">
-        <v>44434</v>
+        <v>45026</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -5166,21 +4911,21 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>22450956</v>
+        <v>10691387</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>MORUA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SERGIO WALTER</t>
+          <t>VICTOR HUGO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5200,29 +4945,29 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 3</t>
         </is>
       </c>
       <c r="I51">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J51">
         <v>2025</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2025-29</t>
+          <t>2025-27</t>
         </is>
       </c>
       <c r="L51" s="2">
-        <v>45882</v>
+        <v>45840</v>
       </c>
       <c r="M51" s="3">
-        <v>45855</v>
+        <v>45838</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5247,17 +4992,17 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Tto en curso</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5273,21 +5018,21 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>32733859</v>
+        <v>5123419</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ACUÑA</t>
+          <t>ALBORNOZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GRISELDA YSABEL</t>
+          <t>JUANA EUSEBIA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5307,25 +5052,25 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>05. Infección resuelta o falso anti VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I52">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J52">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2023-15</t>
+          <t>2024-22</t>
         </is>
       </c>
       <c r="L52" s="2">
-        <v>45063</v>
+        <v>45498</v>
       </c>
       <c r="M52" s="3">
-        <v>45026</v>
+        <v>45440</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -5334,32 +5079,67 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>28060140</v>
+        <v>20897254</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SEQUEIRA</t>
+          <t>MANSILLA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NANCY ELIZABETH</t>
+          <t>SILVIA ALEJANDRA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5383,25 +5163,25 @@
         </is>
       </c>
       <c r="I53">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J53">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2019-34</t>
+          <t>2024-19</t>
         </is>
       </c>
       <c r="L53" s="2">
-        <v>43703</v>
+        <v>45139</v>
       </c>
       <c r="M53" s="3">
-        <v>43700</v>
+        <v>45420</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5436,12 +5216,12 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -5452,16 +5232,16 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>22803266</v>
+        <v>18613513</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MARTINENGO</t>
+          <t>GUENTELICAN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PABLO DIEGO</t>
+          <t>JUAN ANDRES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5486,29 +5266,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I54">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J54">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2019-47</t>
+          <t>2025-33</t>
         </is>
       </c>
       <c r="L54" s="2">
-        <v>43790</v>
+        <v>45883</v>
       </c>
       <c r="M54" s="3">
-        <v>43789</v>
+        <v>45883</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5518,7 +5298,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5538,12 +5318,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Tto en curso</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5559,21 +5339,21 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>24820513</v>
+        <v>27112019</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CRIADO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LORENA STELLA MARIS</t>
+          <t>SELVA BEATRIZ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5593,69 +5373,34 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>06. Caso DESCARTADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I55">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="J55">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2021-52</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="L55" s="2">
-        <v>44557</v>
+        <v>45363</v>
       </c>
       <c r="M55" s="3">
-        <v>44557</v>
+        <v>45348</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -5666,16 +5411,16 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>18853144</v>
+        <v>24580401</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VERA VIDAL</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LAURA ESTER</t>
+          <t>GRACIELA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5700,25 +5445,25 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I56">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J56">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2024-18</t>
+          <t>2023-25</t>
         </is>
       </c>
       <c r="L56" s="2">
-        <v>45565</v>
+        <v>45119</v>
       </c>
       <c r="M56" s="3">
-        <v>45411</v>
+        <v>45098</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -5773,16 +5518,16 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>31931970</v>
+        <v>32473179</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DOS SANTOS TORRES</t>
+          <t>TOBAR GUERRA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LEONARDO DAMIAN</t>
+          <t>CRISTIAN ARTURO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5802,30 +5547,30 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I57">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="J57">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2019-47</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="L57" s="2">
-        <v>43851</v>
+        <v>45240</v>
       </c>
       <c r="M57" s="3">
-        <v>43791</v>
+        <v>44971</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5834,7 +5579,42 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>HIV</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5845,26 +5625,26 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>95120818</v>
+        <v>13744342</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MARTINEZ DIAZ</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RAQUEL</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5879,34 +5659,69 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 3</t>
         </is>
       </c>
       <c r="I58">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2019-43</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="L58" s="2">
-        <v>43864</v>
+        <v>44599</v>
       </c>
       <c r="M58" s="3">
-        <v>43761</v>
+        <v>44595</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -5917,16 +5732,16 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>33992074</v>
+        <v>31615481</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LUNA ROMANO</t>
+          <t>CANCINO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MAXIMILIANO GASTON</t>
+          <t>SILVANA NATALIA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5936,7 +5751,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5951,25 +5766,25 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>07. En estudio para Hepatitis C</t>
+          <t>Virus Hepatitis C, genotipo 1</t>
         </is>
       </c>
       <c r="I59">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="J59">
         <v>2023</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2023-43</t>
+          <t>2023-15</t>
         </is>
       </c>
       <c r="L59" s="2">
-        <v>45275</v>
+        <v>45065</v>
       </c>
       <c r="M59" s="3">
-        <v>45225</v>
+        <v>45027</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5978,7 +5793,42 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
           <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -5989,21 +5839,21 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>92828931</v>
+        <v>27541551</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CATELICAN CARDENAS</t>
+          <t>DURAN</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MARIA OLINDA</t>
+          <t>MARIA VANESA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6023,34 +5873,69 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I60">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J60">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2020-21</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="L60" s="2">
-        <v>43970</v>
+        <v>44628</v>
       </c>
       <c r="M60" s="3">
-        <v>43969</v>
+        <v>44628</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>RIO TERCERO</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -6061,26 +5946,26 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>21352851</v>
+        <v>30566224</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RUIZ VARGAS</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CARLOS RAIMUNDO</t>
+          <t>SILVANA BEATRIZ</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6095,29 +5980,29 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I61">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J61">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2022-26</t>
+          <t>2024-21</t>
         </is>
       </c>
       <c r="L61" s="2">
-        <v>44182</v>
+        <v>45432</v>
       </c>
       <c r="M61" s="3">
-        <v>44743</v>
+        <v>45432</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6127,12 +6012,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -6147,12 +6032,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6162,22 +6047,22 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>24846310</v>
+        <v>22213030</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SANDEZ</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GRISELDA LILIANA</t>
+          <t>NESTOR DAVID</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6187,7 +6072,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6202,25 +6087,25 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I62">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J62">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2023-39</t>
+          <t>2019-46</t>
         </is>
       </c>
       <c r="L62" s="2">
-        <v>45246</v>
+        <v>43803</v>
       </c>
       <c r="M62" s="3">
-        <v>45196</v>
+        <v>43780</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -6229,7 +6114,42 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
           <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -6240,21 +6160,21 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>34375494</v>
+        <v>16711304</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>ACETO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GISELA BEATRIZ</t>
+          <t>SANDRA ELISABET</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6269,39 +6189,74 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>Virus Hepatitis C, genotipo 2</t>
         </is>
       </c>
       <c r="I63">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="J63">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2024-45</t>
+          <t>2020-29</t>
         </is>
       </c>
       <c r="L63" s="2">
-        <v>45617</v>
+        <v>44178</v>
       </c>
       <c r="M63" s="3">
-        <v>45604</v>
+        <v>44025</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -6312,16 +6267,16 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>28010918</v>
+        <v>23611807</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GAMARRA</t>
+          <t>NAPOLEONE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ALICIA ELISABET</t>
+          <t>SILVANA JAQUELINA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6346,34 +6301,69 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1</t>
         </is>
       </c>
       <c r="I64">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J64">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2025-45</t>
+          <t>2023-43</t>
         </is>
       </c>
       <c r="L64" s="2">
-        <v>45968</v>
+        <v>45236</v>
       </c>
       <c r="M64" s="3">
-        <v>45967</v>
+        <v>45225</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -6384,16 +6374,16 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>12448939</v>
+        <v>22355486</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CABALLERO</t>
+          <t>ACERBI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GLORIA MABEL</t>
+          <t>RAUL EDUARDO</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6403,7 +6393,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6418,69 +6408,34 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 2</t>
+          <t>06. Caso DESCARTADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J65">
         <v>2019</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="L65" s="2">
-        <v>43468</v>
+        <v>43627</v>
       </c>
       <c r="M65" s="3">
-        <v>43468</v>
+        <v>43493</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -6491,21 +6446,21 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>16666106</v>
+        <v>5159683</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SELVA NOEMI</t>
+          <t>MARIA MIRTA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6525,29 +6480,29 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I66">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J66">
         <v>2022</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2022-19</t>
+          <t>2022-18</t>
         </is>
       </c>
       <c r="L66" s="2">
-        <v>44705</v>
+        <v>44712</v>
       </c>
       <c r="M66" s="3">
-        <v>44694</v>
+        <v>44686</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6555,29 +6510,34 @@
           <t>SI</t>
         </is>
       </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6587,27 +6547,27 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>14225457</v>
+        <v>12000042</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ARAOZ</t>
+          <t>BUSTOS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ANGEL ANTONIO</t>
+          <t>ERNESTO REYES</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6627,29 +6587,29 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I67">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J67">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2022-16</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="L67" s="2">
-        <v>44712</v>
+        <v>45712</v>
       </c>
       <c r="M67" s="3">
-        <v>44672</v>
+        <v>45705</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6664,7 +6624,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6679,12 +6639,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6700,16 +6660,16 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>25369696</v>
+        <v>94509088</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MACIEL</t>
+          <t>YECGUANCHUY CHAVEZ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CLAUDIO ABEL</t>
+          <t>RAUL ANTONY</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6734,29 +6694,29 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I68">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J68">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2018-26</t>
+          <t>2023-16</t>
         </is>
       </c>
       <c r="L68" s="2">
-        <v>43304</v>
+        <v>45246</v>
       </c>
       <c r="M68" s="3">
-        <v>43277</v>
+        <v>45034</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6766,12 +6726,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6791,7 +6751,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6807,16 +6767,16 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>93492923</v>
+        <v>13964678</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SUA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t>JORGE DANIEL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6836,94 +6796,64 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>06. Caso DESCARTADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I69">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J69">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2022-22</t>
+          <t>2020-14</t>
         </is>
       </c>
       <c r="L69" s="2">
-        <v>44711</v>
+        <v>44082</v>
       </c>
       <c r="M69" s="3">
-        <v>44711</v>
+        <v>43922</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>36733843</v>
+        <v>27817021</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SANCHEZ GILARDI</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VERONICA SOLEDAD</t>
+          <t>ADRIANA MARISA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6938,39 +6868,74 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I70">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="J70">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2020-38</t>
+          <t>2023-21</t>
         </is>
       </c>
       <c r="L70" s="2">
-        <v>44111</v>
+        <v>45240</v>
       </c>
       <c r="M70" s="3">
-        <v>44089</v>
+        <v>45068</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -6981,26 +6946,26 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>13335777</v>
+        <v>14857249</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GUALTIERI</t>
+          <t>ZALAZAR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SILVIA ESTELA</t>
+          <t>CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7015,59 +6980,94 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 3</t>
         </is>
       </c>
       <c r="I71">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J71">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2019-50</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="L71" s="2">
-        <v>43812</v>
+        <v>45707</v>
       </c>
       <c r="M71" s="3">
-        <v>43811</v>
+        <v>45707</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>23627645</v>
+        <v>13986860</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPEHGT</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JORGE ENRIQUE</t>
+          <t>OSCAR JOSE</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7087,29 +7087,29 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>Virus Hepatitis C, genotipo 4</t>
         </is>
       </c>
       <c r="I72">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="J72">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2023-43</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="L72" s="2">
-        <v>45240</v>
+        <v>45498</v>
       </c>
       <c r="M72" s="3">
-        <v>45224</v>
+        <v>45348</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7124,52 +7124,52 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>900590791</v>
+        <v>17642208</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CHRUTOPHE MICHEL</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AUGUIN DARTHENAY</t>
+          <t>SANDRA EDITH</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7194,64 +7194,99 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I73">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J73">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2019-45</t>
+          <t>2017-42</t>
         </is>
       </c>
       <c r="L73" s="2">
-        <v>43775</v>
+        <v>45406</v>
       </c>
       <c r="M73" s="3">
-        <v>43773</v>
+        <v>43027</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>sin dato</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>18084570</v>
+        <v>24880822</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PELAYES</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO</t>
+          <t>MONICA ANDREA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7261,34 +7296,34 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I74">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J74">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2020-22</t>
+          <t>2018-45</t>
         </is>
       </c>
       <c r="L74" s="2">
-        <v>44178</v>
+        <v>43468</v>
       </c>
       <c r="M74" s="3">
-        <v>43980</v>
+        <v>43413</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7303,7 +7338,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7313,17 +7348,17 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7333,22 +7368,22 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>13326219</v>
+        <v>18084570</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>URRUTIA</t>
+          <t>PELAYES</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MIGUEL ESTEBAN</t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7373,29 +7408,29 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I75">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="J75">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2019-42</t>
+          <t>2020-22</t>
         </is>
       </c>
       <c r="L75" s="2">
-        <v>43754</v>
+        <v>44178</v>
       </c>
       <c r="M75" s="3">
-        <v>43753</v>
+        <v>43980</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7410,7 +7445,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -7420,42 +7455,42 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>17642208</v>
+        <v>13326219</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>URRUTIA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SANDRA EDITH</t>
+          <t>MIGUEL ESTEBAN</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7465,7 +7500,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7480,29 +7515,29 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I76">
         <v>42</v>
       </c>
       <c r="J76">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2017-42</t>
+          <t>2019-42</t>
         </is>
       </c>
       <c r="L76" s="2">
-        <v>45406</v>
+        <v>43754</v>
       </c>
       <c r="M76" s="3">
-        <v>43027</v>
+        <v>43753</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7532,7 +7567,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -7553,26 +7588,26 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>24880822</v>
+        <v>92825549</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>NAIPIL BUSTOS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MONICA ANDREA</t>
+          <t>ALEJANDRO VLADIMIR</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7582,7 +7617,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7591,21 +7626,21 @@
         </is>
       </c>
       <c r="I77">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J77">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2018-45</t>
+          <t>2020-41</t>
         </is>
       </c>
       <c r="L77" s="2">
-        <v>43468</v>
+        <v>44178</v>
       </c>
       <c r="M77" s="3">
-        <v>43413</v>
+        <v>44109</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -7619,7 +7654,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -7644,12 +7679,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -7660,16 +7695,16 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>92825549</v>
+        <v>17888898</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NAIPIL BUSTOS</t>
+          <t>NIETO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ALEJANDRO VLADIMIR</t>
+          <t>RAUL ENRIQUE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7694,25 +7729,25 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I78">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="J78">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2020-41</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="L78" s="2">
-        <v>44178</v>
+        <v>44972</v>
       </c>
       <c r="M78" s="3">
-        <v>44109</v>
+        <v>44963</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -7726,7 +7761,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -7767,16 +7802,16 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>17888898</v>
+        <v>14423827</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NIETO</t>
+          <t>CANTERO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>RAUL ENRIQUE</t>
+          <t>LUIS ALBERTO</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7801,29 +7836,29 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I79">
         <v>6</v>
       </c>
       <c r="J79">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="L79" s="2">
-        <v>44972</v>
+        <v>43865</v>
       </c>
       <c r="M79" s="3">
-        <v>44963</v>
+        <v>43865</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7838,7 +7873,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7848,17 +7883,17 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7868,22 +7903,22 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>93633114</v>
+        <v>14135708</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PEREIRA PEREIRA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JOSE ROBINSON</t>
+          <t>LAURA GLADYS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7893,7 +7928,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7908,25 +7943,25 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J80">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="L80" s="2">
-        <v>45065</v>
+        <v>44178</v>
       </c>
       <c r="M80" s="3">
-        <v>44959</v>
+        <v>43902</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -7935,37 +7970,72 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>27519553</v>
+        <v>93633114</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>PEREIRA PEREIRA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PATRICIA MARGARITA</t>
+          <t>JOSE ROBINSON</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7984,21 +8054,21 @@
         </is>
       </c>
       <c r="I81">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J81">
         <v>2023</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="L81" s="2">
         <v>45065</v>
       </c>
       <c r="M81" s="3">
-        <v>45000</v>
+        <v>44959</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -8007,7 +8077,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -8018,16 +8088,16 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>14135708</v>
+        <v>21816819</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>BARRIENTOS VIDAL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LAURA GLADYS</t>
+          <t>LUIS GUILLERMO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -8037,7 +8107,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8052,25 +8122,25 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I82">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="J82">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2023-40</t>
         </is>
       </c>
       <c r="L82" s="2">
-        <v>44178</v>
+        <v>45247</v>
       </c>
       <c r="M82" s="3">
-        <v>43902</v>
+        <v>45204</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -8079,67 +8149,32 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>25116055</v>
+        <v>27519553</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HOYOS</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FABIANA PATRICIA</t>
+          <t>PATRICIA MARGARITA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8159,25 +8194,25 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>07. En estudio para Hepatitis C</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I83">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="J83">
         <v>2023</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2023-44</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="L83" s="2">
-        <v>45236</v>
+        <v>45065</v>
       </c>
       <c r="M83" s="3">
-        <v>45229</v>
+        <v>45000</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -8197,16 +8232,16 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>14423827</v>
+        <v>25116055</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CANTERO</t>
+          <t>HOYOS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>FABIANA PATRICIA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -8216,7 +8251,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8231,94 +8266,59 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>07. En estudio para Hepatitis C</t>
         </is>
       </c>
       <c r="I84">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="J84">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2023-44</t>
         </is>
       </c>
       <c r="L84" s="2">
-        <v>43865</v>
+        <v>45236</v>
       </c>
       <c r="M84" s="3">
-        <v>43865</v>
+        <v>45229</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>21816819</v>
+        <v>34375222</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BARRIENTOS VIDAL</t>
+          <t>MANCILLA MENDEZ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO</t>
+          <t>JORGE DAMIAN</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8333,30 +8333,30 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I85">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J85">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2023-40</t>
+          <t>2025-49</t>
         </is>
       </c>
       <c r="L85" s="2">
-        <v>45247</v>
+        <v>46010</v>
       </c>
       <c r="M85" s="3">
-        <v>45204</v>
+        <v>45996</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -8483,21 +8483,21 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>34375222</v>
+        <v>17438241</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MANCILLA MENDEZ</t>
+          <t>SANTILLAN</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>JORGE DAMIAN</t>
+          <t>HECTOR EDUARDO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8512,30 +8512,30 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>Virus Hepatitis C, genotipo 1</t>
         </is>
       </c>
       <c r="I87">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J87">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2025-49</t>
+          <t>2019-31</t>
         </is>
       </c>
       <c r="L87" s="2">
-        <v>46010</v>
+        <v>43690</v>
       </c>
       <c r="M87" s="3">
-        <v>45996</v>
+        <v>43679</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -8544,7 +8544,42 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -8627,16 +8662,16 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>13844552</v>
+        <v>25006616</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OVANDO</t>
+          <t>PANIAGUA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ROSA ESTHER</t>
+          <t>PAOLA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8661,7 +8696,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I89">
@@ -8676,14 +8711,14 @@
         </is>
       </c>
       <c r="L89" s="2">
-        <v>44833</v>
+        <v>44932</v>
       </c>
       <c r="M89" s="3">
-        <v>44782</v>
+        <v>44781</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8698,7 +8733,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8718,7 +8753,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8734,16 +8769,16 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>25006616</v>
+        <v>13844552</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PANIAGUA</t>
+          <t>OVANDO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PAOLA</t>
+          <t>ROSA ESTHER</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8768,7 +8803,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I90">
@@ -8783,14 +8818,14 @@
         </is>
       </c>
       <c r="L90" s="2">
-        <v>44932</v>
+        <v>44833</v>
       </c>
       <c r="M90" s="3">
-        <v>44781</v>
+        <v>44782</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8805,7 +8840,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8825,7 +8860,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8841,26 +8876,26 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>17438241</v>
+        <v>93744318</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SANTILLAN</t>
+          <t>AGUILA AGUILA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HECTOR EDUARDO</t>
+          <t>MIRNA ADELITA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -8875,25 +8910,25 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I91">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="J91">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2019-31</t>
+          <t>2025-50</t>
         </is>
       </c>
       <c r="L91" s="2">
-        <v>43690</v>
+        <v>46041</v>
       </c>
       <c r="M91" s="3">
-        <v>43679</v>
+        <v>46000</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -8912,7 +8947,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Tto en curso</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8927,12 +8962,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Tto en curso</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8948,21 +8983,21 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>93744318</v>
+        <v>94574916</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AGUILA AGUILA</t>
+          <t>ROA RESQUIN</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MIRNA ADELITA</t>
+          <t>NORMA ELIZABETH</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8982,25 +9017,25 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>05. Infección resuelta o falso anti VHC</t>
         </is>
       </c>
       <c r="I92">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="J92">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2025-50</t>
+          <t>2024-32</t>
         </is>
       </c>
       <c r="L92" s="2">
-        <v>46041</v>
+        <v>45512</v>
       </c>
       <c r="M92" s="3">
-        <v>46000</v>
+        <v>45512</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -9009,42 +9044,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>Tto en curso</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Tto en curso</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -9055,21 +9055,21 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>94574916</v>
+        <v>18265819</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ROA RESQUIN</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NORMA ELIZABETH</t>
+          <t>MARTA GLADYS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9089,25 +9089,25 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>05. Infección resuelta o falso anti VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I93">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J93">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2024-32</t>
+          <t>2025-14</t>
         </is>
       </c>
       <c r="L93" s="2">
-        <v>45512</v>
+        <v>45748</v>
       </c>
       <c r="M93" s="3">
-        <v>45512</v>
+        <v>45748</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -9116,7 +9116,42 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -9127,16 +9162,16 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>18265819</v>
+        <v>21970773</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MARTA GLADYS</t>
+          <t>ROSA RAQUEL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -9161,69 +9196,34 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>06. Caso DESCARTADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I94">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J94">
         <v>2025</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2025-14</t>
+          <t>2025-35</t>
         </is>
       </c>
       <c r="L94" s="2">
-        <v>45748</v>
+        <v>45898</v>
       </c>
       <c r="M94" s="3">
-        <v>45748</v>
+        <v>45897</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
@@ -9234,16 +9234,16 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>21970773</v>
+        <v>20853965</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>BRUNO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ROSA RAQUEL</t>
+          <t>MARCELO FABIAN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -9268,25 +9268,25 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>06. Caso DESCARTADO de Infección por VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I95">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J95">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2025-35</t>
+          <t>2019-38</t>
         </is>
       </c>
       <c r="L95" s="2">
-        <v>45898</v>
+        <v>43754</v>
       </c>
       <c r="M95" s="3">
-        <v>45897</v>
+        <v>43724</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -9295,7 +9295,42 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -9306,26 +9341,26 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>34423562</v>
+        <v>12693857</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GASC</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MARIO LEONARDO</t>
+          <t>OLGA BEATRIZ</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -9344,30 +9379,30 @@
         </is>
       </c>
       <c r="I96">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="J96">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2020-29</t>
+          <t>2018-52</t>
         </is>
       </c>
       <c r="L96" s="2">
-        <v>44176</v>
+        <v>43503</v>
       </c>
       <c r="M96" s="3">
-        <v>44027</v>
+        <v>43461</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
@@ -9378,16 +9413,16 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>33845183</v>
+        <v>34423562</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>GASC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SERGIO ORLANDO</t>
+          <t>MARIO LEONARDO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -9412,69 +9447,34 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I97">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J97">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2023-16</t>
+          <t>2020-29</t>
         </is>
       </c>
       <c r="L97" s="2">
-        <v>45240</v>
+        <v>44176</v>
       </c>
       <c r="M97" s="3">
-        <v>45033</v>
+        <v>44027</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>HIV</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -9485,21 +9485,21 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>33099926</v>
+        <v>8599406</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VILCA</t>
+          <t>ARSELLI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DENIS LEONEL</t>
+          <t>ARMANDO RICARDO</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9523,30 +9523,65 @@
         </is>
       </c>
       <c r="I98">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="J98">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2024-27</t>
         </is>
       </c>
       <c r="L98" s="2">
-        <v>44932</v>
+        <v>45478</v>
       </c>
       <c r="M98" s="3">
-        <v>44573</v>
+        <v>45476</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
           <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
@@ -9557,26 +9592,26 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>12693857</v>
+        <v>33099926</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>VILCA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>OLGA BEATRIZ</t>
+          <t>DENIS LEONEL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -9591,34 +9626,34 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I99">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="J99">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2018-52</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="L99" s="2">
-        <v>43503</v>
+        <v>44932</v>
       </c>
       <c r="M99" s="3">
-        <v>43461</v>
+        <v>44573</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -9629,21 +9664,21 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>8599406</v>
+        <v>33845183</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ARSELLI</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ARMANDO RICARDO</t>
+          <t>SERGIO ORLANDO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9667,25 +9702,25 @@
         </is>
       </c>
       <c r="I100">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J100">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2024-27</t>
+          <t>2023-16</t>
         </is>
       </c>
       <c r="L100" s="2">
-        <v>45478</v>
+        <v>45240</v>
       </c>
       <c r="M100" s="3">
-        <v>45476</v>
+        <v>45033</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -9695,12 +9730,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9710,132 +9745,25 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>20853965</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>BRUNO</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>MARCELO FABIAN</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>De 45 a 65 años</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
-        </is>
-      </c>
-      <c r="I101">
-        <v>38</v>
-      </c>
-      <c r="J101">
-        <v>2019</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>2019-38</t>
-        </is>
-      </c>
-      <c r="L101" s="2">
-        <v>43754</v>
-      </c>
-      <c r="M101" s="3">
-        <v>43724</v>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>USHUAIA</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
         <is>
           <t>NO</t>
         </is>

--- a/Salidas/data_C_completa.xlsx
+++ b/Salidas/data_C_completa.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W100"/>
+  <dimension ref="A1:W99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="12" max="12" width="20.7109375" style="2" customWidth="1"/>
@@ -7160,21 +7160,21 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>17642208</v>
+        <v>24880822</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SANDRA EDITH</t>
+          <t>MONICA ANDREA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7189,34 +7189,34 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I73">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J73">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2017-42</t>
+          <t>2018-45</t>
         </is>
       </c>
       <c r="L73" s="2">
-        <v>45406</v>
+        <v>43468</v>
       </c>
       <c r="M73" s="3">
-        <v>43027</v>
+        <v>43413</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7246,17 +7246,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -7267,26 +7267,26 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>24880822</v>
+        <v>18084570</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PELAYES</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MONICA ANDREA</t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7296,34 +7296,34 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I74">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J74">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2018-45</t>
+          <t>2020-22</t>
         </is>
       </c>
       <c r="L74" s="2">
-        <v>43468</v>
+        <v>44178</v>
       </c>
       <c r="M74" s="3">
-        <v>43413</v>
+        <v>43980</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7348,17 +7348,17 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7368,22 +7368,22 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>18084570</v>
+        <v>13326219</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PELAYES</t>
+          <t>URRUTIA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO</t>
+          <t>MIGUEL ESTEBAN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7408,29 +7408,29 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I75">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J75">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2020-22</t>
+          <t>2019-42</t>
         </is>
       </c>
       <c r="L75" s="2">
-        <v>44178</v>
+        <v>43754</v>
       </c>
       <c r="M75" s="3">
-        <v>43980</v>
+        <v>43753</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -7455,42 +7455,42 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>13326219</v>
+        <v>92825549</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>URRUTIA</t>
+          <t>NAIPIL BUSTOS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MIGUEL ESTEBAN</t>
+          <t>ALEJANDRO VLADIMIR</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7515,25 +7515,25 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I76">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J76">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2019-42</t>
+          <t>2020-41</t>
         </is>
       </c>
       <c r="L76" s="2">
-        <v>43754</v>
+        <v>44178</v>
       </c>
       <c r="M76" s="3">
-        <v>43753</v>
+        <v>44109</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -7588,16 +7588,16 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>92825549</v>
+        <v>17888898</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NAIPIL BUSTOS</t>
+          <t>NIETO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ALEJANDRO VLADIMIR</t>
+          <t>RAUL ENRIQUE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7622,25 +7622,25 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I77">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="J77">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2020-41</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="L77" s="2">
-        <v>44178</v>
+        <v>44972</v>
       </c>
       <c r="M77" s="3">
-        <v>44109</v>
+        <v>44963</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -7695,16 +7695,16 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>17888898</v>
+        <v>14423827</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NIETO</t>
+          <t>CANTERO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>RAUL ENRIQUE</t>
+          <t>LUIS ALBERTO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7729,29 +7729,29 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I78">
         <v>6</v>
       </c>
       <c r="J78">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="L78" s="2">
-        <v>44972</v>
+        <v>43865</v>
       </c>
       <c r="M78" s="3">
-        <v>44963</v>
+        <v>43865</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7776,17 +7776,17 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7796,22 +7796,22 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>14423827</v>
+        <v>14135708</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CANTERO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>LAURA GLADYS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7836,29 +7836,29 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I79">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J79">
         <v>2020</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="L79" s="2">
-        <v>43865</v>
+        <v>44178</v>
       </c>
       <c r="M79" s="3">
-        <v>43865</v>
+        <v>43902</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7883,22 +7883,22 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -7909,16 +7909,16 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>14135708</v>
+        <v>93633114</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PEREIRA PEREIRA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LAURA GLADYS</t>
+          <t>JOSE ROBINSON</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7943,25 +7943,25 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I80">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J80">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="L80" s="2">
-        <v>44178</v>
+        <v>45065</v>
       </c>
       <c r="M80" s="3">
-        <v>43902</v>
+        <v>44959</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -7970,62 +7970,27 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>93633114</v>
+        <v>21816819</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PEREIRA PEREIRA</t>
+          <t>BARRIENTOS VIDAL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>JOSE ROBINSON</t>
+          <t>LUIS GUILLERMO</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -8054,21 +8019,21 @@
         </is>
       </c>
       <c r="I81">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="J81">
         <v>2023</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-40</t>
         </is>
       </c>
       <c r="L81" s="2">
-        <v>45065</v>
+        <v>45247</v>
       </c>
       <c r="M81" s="3">
-        <v>44959</v>
+        <v>45204</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -8077,7 +8042,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -8088,26 +8053,26 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>21816819</v>
+        <v>27519553</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BARRIENTOS VIDAL</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO</t>
+          <t>PATRICIA MARGARITA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8126,21 +8091,21 @@
         </is>
       </c>
       <c r="I82">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="J82">
         <v>2023</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2023-40</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="L82" s="2">
-        <v>45247</v>
+        <v>45065</v>
       </c>
       <c r="M82" s="3">
-        <v>45204</v>
+        <v>45000</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -8160,21 +8125,21 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>27519553</v>
+        <v>25116055</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>HOYOS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PATRICIA MARGARITA</t>
+          <t>FABIANA PATRICIA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8194,25 +8159,25 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>07. En estudio para Hepatitis C</t>
         </is>
       </c>
       <c r="I83">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="J83">
         <v>2023</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-44</t>
         </is>
       </c>
       <c r="L83" s="2">
-        <v>45065</v>
+        <v>45236</v>
       </c>
       <c r="M83" s="3">
-        <v>45000</v>
+        <v>45229</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -8232,26 +8197,26 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>25116055</v>
+        <v>34375222</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HOYOS</t>
+          <t>MANCILLA MENDEZ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FABIANA PATRICIA</t>
+          <t>JORGE DAMIAN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8261,30 +8226,30 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>07. En estudio para Hepatitis C</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I84">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J84">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2023-44</t>
+          <t>2025-49</t>
         </is>
       </c>
       <c r="L84" s="2">
-        <v>45236</v>
+        <v>46010</v>
       </c>
       <c r="M84" s="3">
-        <v>45229</v>
+        <v>45996</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -8304,21 +8269,21 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>34375222</v>
+        <v>22668469</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MANCILLA MENDEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JORGE DAMIAN</t>
+          <t>JULIO ARNALDO PABLO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8333,30 +8298,30 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I85">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J85">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2025-49</t>
+          <t>2023-44</t>
         </is>
       </c>
       <c r="L85" s="2">
-        <v>46010</v>
+        <v>45236</v>
       </c>
       <c r="M85" s="3">
-        <v>45996</v>
+        <v>45233</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -8365,27 +8330,62 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
           <t>SIN DATOS</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>22668469</v>
+        <v>17438241</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>SANTILLAN</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>JULIO ARNALDO PABLO</t>
+          <t>HECTOR EDUARDO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -8410,25 +8410,25 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>Virus Hepatitis C, genotipo 1</t>
         </is>
       </c>
       <c r="I86">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="J86">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2023-44</t>
+          <t>2019-31</t>
         </is>
       </c>
       <c r="L86" s="2">
-        <v>45236</v>
+        <v>43690</v>
       </c>
       <c r="M86" s="3">
-        <v>45233</v>
+        <v>43679</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -8447,52 +8447,52 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>17438241</v>
+        <v>20066627</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SANTILLAN</t>
+          <t>MASI</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HECTOR EDUARDO</t>
+          <t>CLAUDIA ESTER</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8517,25 +8517,25 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I87">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J87">
         <v>2019</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2019-31</t>
+          <t>2019-13</t>
         </is>
       </c>
       <c r="L87" s="2">
-        <v>43690</v>
+        <v>44923</v>
       </c>
       <c r="M87" s="3">
-        <v>43679</v>
+        <v>43550</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -8544,42 +8544,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -8590,16 +8555,16 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>20066627</v>
+        <v>25006616</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MASI</t>
+          <t>PANIAGUA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CLAUDIA ESTER</t>
+          <t>PAOLA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8624,25 +8589,25 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I88">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="J88">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2019-13</t>
+          <t>2022-32</t>
         </is>
       </c>
       <c r="L88" s="2">
-        <v>44923</v>
+        <v>44932</v>
       </c>
       <c r="M88" s="3">
-        <v>43550</v>
+        <v>44781</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -8651,7 +8616,42 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -8662,16 +8662,16 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>25006616</v>
+        <v>13844552</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PANIAGUA</t>
+          <t>OVANDO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PAOLA</t>
+          <t>ROSA ESTHER</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I89">
@@ -8711,14 +8711,14 @@
         </is>
       </c>
       <c r="L89" s="2">
-        <v>44932</v>
+        <v>44833</v>
       </c>
       <c r="M89" s="3">
-        <v>44781</v>
+        <v>44782</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8769,21 +8769,21 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>13844552</v>
+        <v>93744318</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OVANDO</t>
+          <t>AGUILA AGUILA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ROSA ESTHER</t>
+          <t>MIRNA ADELITA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8803,29 +8803,29 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I90">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="J90">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2022-32</t>
+          <t>2025-50</t>
         </is>
       </c>
       <c r="L90" s="2">
-        <v>44833</v>
+        <v>46041</v>
       </c>
       <c r="M90" s="3">
-        <v>44782</v>
+        <v>46000</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Tto en curso</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Tto en curso</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -8876,21 +8876,21 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>93744318</v>
+        <v>94574916</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AGUILA AGUILA</t>
+          <t>ROA RESQUIN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MIRNA ADELITA</t>
+          <t>NORMA ELIZABETH</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8910,25 +8910,25 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>05. Infección resuelta o falso anti VHC</t>
         </is>
       </c>
       <c r="I91">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="J91">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2025-50</t>
+          <t>2024-32</t>
         </is>
       </c>
       <c r="L91" s="2">
-        <v>46041</v>
+        <v>45512</v>
       </c>
       <c r="M91" s="3">
-        <v>46000</v>
+        <v>45512</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -8937,42 +8937,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>Tto en curso</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Tto en curso</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -8983,21 +8948,21 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>94574916</v>
+        <v>18265819</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ROA RESQUIN</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NORMA ELIZABETH</t>
+          <t>MARTA GLADYS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9017,25 +8982,25 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>05. Infección resuelta o falso anti VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I92">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J92">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2024-32</t>
+          <t>2025-14</t>
         </is>
       </c>
       <c r="L92" s="2">
-        <v>45512</v>
+        <v>45748</v>
       </c>
       <c r="M92" s="3">
-        <v>45512</v>
+        <v>45748</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -9044,7 +9009,42 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -9055,16 +9055,16 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>18265819</v>
+        <v>21970773</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MARTA GLADYS</t>
+          <t>ROSA RAQUEL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9089,69 +9089,34 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>06. Caso DESCARTADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I93">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J93">
         <v>2025</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2025-14</t>
+          <t>2025-35</t>
         </is>
       </c>
       <c r="L93" s="2">
-        <v>45748</v>
+        <v>45898</v>
       </c>
       <c r="M93" s="3">
-        <v>45748</v>
+        <v>45897</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -9162,16 +9127,16 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>21970773</v>
+        <v>20853965</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>BRUNO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ROSA RAQUEL</t>
+          <t>MARCELO FABIAN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -9181,7 +9146,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -9196,25 +9161,25 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>06. Caso DESCARTADO de Infección por VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I94">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J94">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2025-35</t>
+          <t>2019-38</t>
         </is>
       </c>
       <c r="L94" s="2">
-        <v>45898</v>
+        <v>43754</v>
       </c>
       <c r="M94" s="3">
-        <v>45897</v>
+        <v>43724</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -9223,7 +9188,42 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
@@ -9234,16 +9234,16 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>20853965</v>
+        <v>12693857</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BRUNO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>OLGA BEATRIZ</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -9268,69 +9268,34 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I95">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J95">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2019-38</t>
+          <t>2018-52</t>
         </is>
       </c>
       <c r="L95" s="2">
-        <v>43754</v>
+        <v>43503</v>
       </c>
       <c r="M95" s="3">
-        <v>43724</v>
+        <v>43461</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -9341,26 +9306,26 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>12693857</v>
+        <v>34423562</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>GASC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OLGA BEATRIZ</t>
+          <t>MARIO LEONARDO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -9379,30 +9344,30 @@
         </is>
       </c>
       <c r="I96">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="J96">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2018-52</t>
+          <t>2020-29</t>
         </is>
       </c>
       <c r="L96" s="2">
-        <v>43503</v>
+        <v>44176</v>
       </c>
       <c r="M96" s="3">
-        <v>43461</v>
+        <v>44027</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
@@ -9413,21 +9378,21 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>34423562</v>
+        <v>8599406</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GASC</t>
+          <t>ARSELLI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MARIO LEONARDO</t>
+          <t>ARMANDO RICARDO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9447,25 +9412,25 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I97">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J97">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2020-29</t>
+          <t>2024-27</t>
         </is>
       </c>
       <c r="L97" s="2">
-        <v>44176</v>
+        <v>45478</v>
       </c>
       <c r="M97" s="3">
-        <v>44027</v>
+        <v>45476</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -9474,7 +9439,42 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
           <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -9485,21 +9485,21 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>8599406</v>
+        <v>33099926</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ARSELLI</t>
+          <t>VILCA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ARMANDO RICARDO</t>
+          <t>DENIS LEONEL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9523,65 +9523,30 @@
         </is>
       </c>
       <c r="I98">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="J98">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2024-27</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="L98" s="2">
-        <v>45478</v>
+        <v>44932</v>
       </c>
       <c r="M98" s="3">
-        <v>45476</v>
+        <v>44573</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
           <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
@@ -9592,21 +9557,21 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>33099926</v>
+        <v>33845183</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VILCA</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DENIS LEONEL</t>
+          <t>SERGIO ORLANDO</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9630,21 +9595,21 @@
         </is>
       </c>
       <c r="I99">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J99">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2023-16</t>
         </is>
       </c>
       <c r="L99" s="2">
-        <v>44932</v>
+        <v>45240</v>
       </c>
       <c r="M99" s="3">
-        <v>44573</v>
+        <v>45033</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -9653,117 +9618,45 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>HIV</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100">
-        <v>33845183</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>MORA</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>SERGIO ORLANDO</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>De 25 a 34 años</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Hepatitis virales</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
-        </is>
-      </c>
-      <c r="I100">
-        <v>16</v>
-      </c>
-      <c r="J100">
-        <v>2023</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>2023-16</t>
-        </is>
-      </c>
-      <c r="L100" s="2">
-        <v>45240</v>
-      </c>
-      <c r="M100" s="3">
-        <v>45033</v>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>USHUAIA</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>HIV</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>

--- a/Salidas/data_C_completa.xlsx
+++ b/Salidas/data_C_completa.xlsx
@@ -483,21 +483,21 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>6729312</v>
+        <v>93329075</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SANCHEZ DELGADO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ROSA JUANA</t>
+          <t>BERTA PATRICIA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -517,25 +517,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1</t>
         </is>
       </c>
       <c r="I2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="J2">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2018-32</t>
+          <t>2025-44</t>
         </is>
       </c>
       <c r="L2" s="2">
-        <v>43405</v>
+        <v>46003</v>
       </c>
       <c r="M2" s="3">
-        <v>43319</v>
+        <v>45960</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -554,52 +554,52 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>Tto en curso</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>93329075</v>
+        <v>93060680</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANCHEZ DELGADO</t>
+          <t>MIGUEZ OCHOA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BERTA PATRICIA</t>
+          <t>SANDRA ROSSANA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -624,29 +624,29 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2025-44</t>
+          <t>2024-45</t>
         </is>
       </c>
       <c r="L3" s="2">
-        <v>46003</v>
+        <v>45616</v>
       </c>
       <c r="M3" s="3">
-        <v>45960</v>
+        <v>45603</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Tto en curso</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -697,16 +697,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>93060680</v>
+        <v>32822988</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MIGUEZ OCHOA</t>
+          <t>AGUERO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SANDRA ROSSANA</t>
+          <t>WALTER ALBERTO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -735,65 +735,30 @@
         </is>
       </c>
       <c r="I4">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="J4">
         <v>2024</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2024-45</t>
+          <t>2024-31</t>
         </is>
       </c>
       <c r="L4" s="2">
-        <v>45616</v>
+        <v>45506</v>
       </c>
       <c r="M4" s="3">
-        <v>45603</v>
+        <v>45503</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -804,26 +769,26 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>32822988</v>
+        <v>6729312</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AGUERO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WALTER ALBERTO</t>
+          <t>ROSA JUANA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -842,21 +807,21 @@
         </is>
       </c>
       <c r="I5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J5">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2024-31</t>
+          <t>2018-32</t>
         </is>
       </c>
       <c r="L5" s="2">
-        <v>45506</v>
+        <v>43405</v>
       </c>
       <c r="M5" s="3">
-        <v>45503</v>
+        <v>43319</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -865,12 +830,47 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>SIN DATOS</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>16013397</v>
+        <v>17168769</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OLIVERO</t>
+          <t>GERON</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLAUDIA MARCELA</t>
+          <t>JUAN DOMINGO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1303,29 +1303,29 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 2</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I10">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J10">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2022-51</t>
+          <t>2024-45</t>
         </is>
       </c>
       <c r="L10" s="2">
-        <v>44972</v>
+        <v>44655</v>
       </c>
       <c r="M10" s="3">
-        <v>44916</v>
+        <v>45601</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1376,16 +1376,16 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>17168769</v>
+        <v>16013397</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GERON</t>
+          <t>OLIVERO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JUAN DOMINGO</t>
+          <t>CLAUDIA MARCELA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1410,29 +1410,29 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 2</t>
         </is>
       </c>
       <c r="I11">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J11">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2024-45</t>
+          <t>2022-51</t>
         </is>
       </c>
       <c r="L11" s="2">
-        <v>44655</v>
+        <v>44972</v>
       </c>
       <c r="M11" s="3">
-        <v>45601</v>
+        <v>44916</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1662,26 +1662,26 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>10629822</v>
+        <v>27207402</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>HUERTAS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OSVALDO MARIO</t>
+          <t>AMANDA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1696,25 +1696,25 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>05. Infección resuelta o falso anti VHC</t>
         </is>
       </c>
       <c r="I14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J14">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2022-48</t>
+          <t>2023-49</t>
         </is>
       </c>
       <c r="L14" s="2">
-        <v>44923</v>
+        <v>45265</v>
       </c>
       <c r="M14" s="3">
-        <v>44894</v>
+        <v>45265</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1734,26 +1734,26 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>27207402</v>
+        <v>10629822</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HUERTAS</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AMANDA</t>
+          <t>OSVALDO MARIO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1768,25 +1768,25 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>05. Infección resuelta o falso anti VHC</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I15">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J15">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2023-49</t>
+          <t>2022-48</t>
         </is>
       </c>
       <c r="L15" s="2">
-        <v>45265</v>
+        <v>44923</v>
       </c>
       <c r="M15" s="3">
-        <v>45265</v>
+        <v>44894</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>34113677</v>
+        <v>39939562</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ABALLAY</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PAMELA NOEMI</t>
+          <t>MICAELA SILVIA VANESSA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1947,29 +1947,29 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>07. En estudio para Hepatitis C</t>
         </is>
       </c>
       <c r="I17">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J17">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2023-44</t>
+          <t>2021-47</t>
         </is>
       </c>
       <c r="L17" s="2">
-        <v>45240</v>
+        <v>44539</v>
       </c>
       <c r="M17" s="3">
-        <v>45230</v>
+        <v>44526</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1985,16 +1985,16 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>39939562</v>
+        <v>34113677</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>ABALLAY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MICAELA SILVIA VANESSA</t>
+          <t>PAMELA NOEMI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2019,29 +2019,29 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>07. En estudio para Hepatitis C</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I18">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J18">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2021-47</t>
+          <t>2023-44</t>
         </is>
       </c>
       <c r="L18" s="2">
-        <v>44539</v>
+        <v>45240</v>
       </c>
       <c r="M18" s="3">
-        <v>44526</v>
+        <v>45230</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2129,16 +2129,16 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>23273835</v>
+        <v>25319717</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>OROPEL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GUSTAVO ARIEL</t>
+          <t>HIPOLITO LUJAN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2163,39 +2163,74 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I20">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2024-30</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="L20" s="2">
-        <v>45565</v>
+        <v>44628</v>
       </c>
       <c r="M20" s="3">
-        <v>45498</v>
+        <v>44995</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2308,16 +2343,16 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>25319717</v>
+        <v>23273835</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OROPEL</t>
+          <t>BARRETO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HIPOLITO LUJAN</t>
+          <t>GUSTAVO ARIEL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2342,99 +2377,64 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I22">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J22">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-30</t>
         </is>
       </c>
       <c r="L22" s="2">
-        <v>44628</v>
+        <v>45565</v>
       </c>
       <c r="M22" s="3">
-        <v>44995</v>
+        <v>45498</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>22667988</v>
+        <v>35985565</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ABAGNALE</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SERGIO GABRIEL</t>
+          <t>DAIANA BEATRIZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2453,21 +2453,21 @@
         </is>
       </c>
       <c r="I23">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J23">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2021-34</t>
+          <t>2023-24</t>
         </is>
       </c>
       <c r="L23" s="2">
-        <v>44473</v>
+        <v>45121</v>
       </c>
       <c r="M23" s="3">
-        <v>44434</v>
+        <v>45092</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2487,26 +2487,26 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>35985565</v>
+        <v>22667988</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>ABAGNALE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DAIANA BEATRIZ</t>
+          <t>SERGIO GABRIEL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="I24">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J24">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2023-24</t>
+          <t>2021-34</t>
         </is>
       </c>
       <c r="L24" s="2">
-        <v>45121</v>
+        <v>44473</v>
       </c>
       <c r="M24" s="3">
-        <v>45092</v>
+        <v>44434</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2559,26 +2559,26 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>28060140</v>
+        <v>22803266</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SEQUEIRA</t>
+          <t>MARTINENGO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NANCY ELIZABETH</t>
+          <t>PABLO DIEGO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2597,25 +2597,25 @@
         </is>
       </c>
       <c r="I25">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="J25">
         <v>2019</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2019-34</t>
+          <t>2019-47</t>
         </is>
       </c>
       <c r="L25" s="2">
-        <v>43703</v>
+        <v>43790</v>
       </c>
       <c r="M25" s="3">
-        <v>43700</v>
+        <v>43789</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2666,26 +2666,26 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>22803266</v>
+        <v>28060140</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MARTINENGO</t>
+          <t>SEQUEIRA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PABLO DIEGO</t>
+          <t>NANCY ELIZABETH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="I26">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J26">
         <v>2019</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2019-47</t>
+          <t>2019-34</t>
         </is>
       </c>
       <c r="L26" s="2">
-        <v>43790</v>
+        <v>43703</v>
       </c>
       <c r="M26" s="3">
-        <v>43789</v>
+        <v>43700</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2845,16 +2845,16 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>24820513</v>
+        <v>18853144</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CRIADO</t>
+          <t>VERA VIDAL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LORENA STELLA MARIS</t>
+          <t>LAURA ESTER</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2883,25 +2883,25 @@
         </is>
       </c>
       <c r="I28">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J28">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2021-52</t>
+          <t>2024-18</t>
         </is>
       </c>
       <c r="L28" s="2">
-        <v>44557</v>
+        <v>45565</v>
       </c>
       <c r="M28" s="3">
-        <v>44557</v>
+        <v>45411</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2952,16 +2952,16 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>18853144</v>
+        <v>24820513</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VERA VIDAL</t>
+          <t>CRIADO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LAURA ESTER</t>
+          <t>LORENA STELLA MARIS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2990,25 +2990,25 @@
         </is>
       </c>
       <c r="I29">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="J29">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2024-18</t>
+          <t>2021-52</t>
         </is>
       </c>
       <c r="L29" s="2">
-        <v>45565</v>
+        <v>44557</v>
       </c>
       <c r="M29" s="3">
-        <v>45411</v>
+        <v>44557</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3275,16 +3275,16 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>21352851</v>
+        <v>22450956</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RUIZ VARGAS</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CARLOS RAIMUNDO</t>
+          <t>SERGIO WALTER</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3313,21 +3313,21 @@
         </is>
       </c>
       <c r="I33">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J33">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2022-26</t>
+          <t>2025-29</t>
         </is>
       </c>
       <c r="L33" s="2">
-        <v>44182</v>
+        <v>45882</v>
       </c>
       <c r="M33" s="3">
-        <v>44743</v>
+        <v>45855</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3376,22 +3376,22 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>24846310</v>
+        <v>21352851</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SANDEZ</t>
+          <t>RUIZ VARGAS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GRISELDA LILIANA</t>
+          <t>CARLOS RAIMUNDO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3416,25 +3416,25 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I34">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="J34">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2023-39</t>
+          <t>2022-26</t>
         </is>
       </c>
       <c r="L34" s="2">
-        <v>45246</v>
+        <v>44182</v>
       </c>
       <c r="M34" s="3">
-        <v>45196</v>
+        <v>44743</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3443,37 +3443,72 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>28010918</v>
+        <v>33992074</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GAMARRA</t>
+          <t>LUNA ROMANO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ALICIA ELISABET</t>
+          <t>MAXIMILIANO GASTON</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3488,34 +3523,34 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>07. En estudio para Hepatitis C</t>
         </is>
       </c>
       <c r="I35">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J35">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2025-45</t>
+          <t>2023-43</t>
         </is>
       </c>
       <c r="L35" s="2">
-        <v>45968</v>
+        <v>45275</v>
       </c>
       <c r="M35" s="3">
-        <v>45967</v>
+        <v>45225</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -3526,26 +3561,26 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>33992074</v>
+        <v>28010918</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LUNA ROMANO</t>
+          <t>GAMARRA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MAXIMILIANO GASTON</t>
+          <t>ALICIA ELISABET</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3560,34 +3595,34 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>07. En estudio para Hepatitis C</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I36">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J36">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2023-43</t>
+          <t>2025-45</t>
         </is>
       </c>
       <c r="L36" s="2">
-        <v>45275</v>
+        <v>45968</v>
       </c>
       <c r="M36" s="3">
-        <v>45225</v>
+        <v>45967</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -3598,21 +3633,21 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>34375494</v>
+        <v>92828931</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CATELICAN CARDENAS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GISELA BEATRIZ</t>
+          <t>MARIA OLINDA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3627,30 +3662,30 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>02. Caso sospechoso en banco de sangre</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I37">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="J37">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2024-45</t>
+          <t>2020-21</t>
         </is>
       </c>
       <c r="L37" s="2">
-        <v>45617</v>
+        <v>43970</v>
       </c>
       <c r="M37" s="3">
-        <v>45604</v>
+        <v>43969</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3670,16 +3705,16 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>92828931</v>
+        <v>24846310</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CATELICAN CARDENAS</t>
+          <t>SANDEZ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MARIA OLINDA</t>
+          <t>GRISELDA LILIANA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3708,21 +3743,21 @@
         </is>
       </c>
       <c r="I38">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="J38">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2020-21</t>
+          <t>2023-39</t>
         </is>
       </c>
       <c r="L38" s="2">
-        <v>43970</v>
+        <v>45246</v>
       </c>
       <c r="M38" s="3">
-        <v>43969</v>
+        <v>45196</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -3731,7 +3766,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -3742,26 +3777,26 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>22450956</v>
+        <v>34375494</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SERGIO WALTER</t>
+          <t>GISELA BEATRIZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3771,30 +3806,30 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>02. Caso sospechoso en banco de sangre</t>
         </is>
       </c>
       <c r="I39">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="J39">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2025-29</t>
+          <t>2024-45</t>
         </is>
       </c>
       <c r="L39" s="2">
-        <v>45882</v>
+        <v>45617</v>
       </c>
       <c r="M39" s="3">
-        <v>45855</v>
+        <v>45604</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -3803,42 +3838,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -3849,26 +3849,26 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>16666106</v>
+        <v>25369696</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MACIEL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SELVA NOEMI</t>
+          <t>CLAUDIO ABEL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3887,25 +3887,25 @@
         </is>
       </c>
       <c r="I40">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J40">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2022-19</t>
+          <t>2018-26</t>
         </is>
       </c>
       <c r="L40" s="2">
-        <v>44705</v>
+        <v>43304</v>
       </c>
       <c r="M40" s="3">
-        <v>44694</v>
+        <v>43277</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3913,29 +3913,34 @@
           <t>SI</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -3945,22 +3950,22 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>14225457</v>
+        <v>93492923</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ARAOZ</t>
+          <t>SUA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ANGEL ANTONIO</t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3989,25 +3994,25 @@
         </is>
       </c>
       <c r="I41">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J41">
         <v>2022</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2022-16</t>
+          <t>2022-22</t>
         </is>
       </c>
       <c r="L41" s="2">
-        <v>44712</v>
+        <v>44711</v>
       </c>
       <c r="M41" s="3">
-        <v>44672</v>
+        <v>44711</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4037,7 +4042,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4045,29 +4050,24 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>12448939</v>
+        <v>14225457</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CABALLERO</t>
+          <t>ARAOZ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GLORIA MABEL</t>
+          <t>ANGEL ANTONIO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4092,29 +4092,29 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 2</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J42">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2022-16</t>
         </is>
       </c>
       <c r="L42" s="2">
-        <v>43468</v>
+        <v>44712</v>
       </c>
       <c r="M42" s="3">
-        <v>43468</v>
+        <v>44672</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -4165,26 +4165,26 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>25369696</v>
+        <v>16666106</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MACIEL</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CLAUDIO ABEL</t>
+          <t>SELVA NOEMI</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4203,25 +4203,25 @@
         </is>
       </c>
       <c r="I43">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J43">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2018-26</t>
+          <t>2022-19</t>
         </is>
       </c>
       <c r="L43" s="2">
-        <v>43304</v>
+        <v>44705</v>
       </c>
       <c r="M43" s="3">
-        <v>43277</v>
+        <v>44694</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>*sin dato*</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4229,34 +4229,29 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4266,22 +4261,22 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>93492923</v>
+        <v>12448939</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SUA</t>
+          <t>CABALLERO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t>GLORIA MABEL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4291,7 +4286,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4306,29 +4301,29 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>Virus Hepatitis C, genotipo 2</t>
         </is>
       </c>
       <c r="I44">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J44">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2022-22</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="L44" s="2">
-        <v>44711</v>
+        <v>43468</v>
       </c>
       <c r="M44" s="3">
-        <v>44711</v>
+        <v>43468</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>*sin dato*</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4358,7 +4353,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -4366,29 +4361,34 @@
           <t>SI</t>
         </is>
       </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>36733843</v>
+        <v>30339686</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SANCHEZ GILARDI</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VERONICA SOLEDAD</t>
+          <t>VIVIANA ELISA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4403,39 +4403,74 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I45">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J45">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2020-38</t>
+          <t>2025-37</t>
         </is>
       </c>
       <c r="L45" s="2">
-        <v>44111</v>
+        <v>45910</v>
       </c>
       <c r="M45" s="3">
-        <v>44089</v>
+        <v>45910</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -4446,26 +4481,26 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>900590791</v>
+        <v>36733843</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CHRUTOPHE MICHEL</t>
+          <t>SANCHEZ GILARDI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AUGUIN DARTHENAY</t>
+          <t>VERONICA SOLEDAD</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4475,69 +4510,69 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I46">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J46">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2019-45</t>
+          <t>2020-38</t>
         </is>
       </c>
       <c r="L46" s="2">
-        <v>43775</v>
+        <v>44111</v>
       </c>
       <c r="M46" s="3">
-        <v>43773</v>
+        <v>44089</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>sin dato</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>13335777</v>
+        <v>900590791</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GUALTIERI</t>
+          <t>CHRUTOPHE MICHEL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SILVIA ESTELA</t>
+          <t>AUGUIN DARTHENAY</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4556,25 +4591,25 @@
         </is>
       </c>
       <c r="I47">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J47">
         <v>2019</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2019-50</t>
+          <t>2019-45</t>
         </is>
       </c>
       <c r="L47" s="2">
-        <v>43812</v>
+        <v>43775</v>
       </c>
       <c r="M47" s="3">
-        <v>43811</v>
+        <v>43773</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4584,32 +4619,32 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>sin dato</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>30339686</v>
+        <v>23627645</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>SPEHGT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VIVIANA ELISA</t>
+          <t>JORGE ENRIQUE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4624,25 +4659,25 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I48">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J48">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2025-37</t>
+          <t>2023-43</t>
         </is>
       </c>
       <c r="L48" s="2">
-        <v>45910</v>
+        <v>45240</v>
       </c>
       <c r="M48" s="3">
-        <v>45910</v>
+        <v>45224</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4676,7 +4711,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -4697,26 +4732,26 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>23627645</v>
+        <v>13335777</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SPEHGT</t>
+          <t>GUALTIERI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>JORGE ENRIQUE</t>
+          <t>SILVIA ESTELA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4731,89 +4766,54 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I49">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J49">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2023-43</t>
+          <t>2019-50</t>
         </is>
       </c>
       <c r="L49" s="2">
-        <v>45240</v>
+        <v>43812</v>
       </c>
       <c r="M49" s="3">
-        <v>45224</v>
+        <v>43811</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>23851558</v>
+        <v>18084570</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>PELAYES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ANTONIO AUGUSTO</t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4838,29 +4838,29 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I50">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J50">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2023-15</t>
+          <t>2020-22</t>
         </is>
       </c>
       <c r="L50" s="2">
-        <v>45239</v>
+        <v>44178</v>
       </c>
       <c r="M50" s="3">
-        <v>45026</v>
+        <v>43980</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4885,47 +4885,47 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>10691387</v>
+        <v>92825549</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MORUA</t>
+          <t>NAIPIL BUSTOS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VICTOR HUGO</t>
+          <t>ALEJANDRO VLADIMIR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4945,25 +4945,25 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 3</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I51">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J51">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2025-27</t>
+          <t>2020-41</t>
         </is>
       </c>
       <c r="L51" s="2">
-        <v>45840</v>
+        <v>44178</v>
       </c>
       <c r="M51" s="3">
-        <v>45838</v>
+        <v>44109</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4992,17 +4992,17 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Tto en curso</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5018,21 +5018,21 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>5123419</v>
+        <v>24880822</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ALBORNOZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JUANA EUSEBIA</t>
+          <t>MONICA ANDREA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5047,34 +5047,34 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I52">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J52">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2024-22</t>
+          <t>2018-45</t>
         </is>
       </c>
       <c r="L52" s="2">
-        <v>45498</v>
+        <v>43468</v>
       </c>
       <c r="M52" s="3">
-        <v>45440</v>
+        <v>43413</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5089,52 +5089,52 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
           <t>SIN DATOS</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>20897254</v>
+        <v>13326219</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MANSILLA</t>
+          <t>URRUTIA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SILVIA ALEJANDRA</t>
+          <t>MIGUEL ESTEBAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5159,29 +5159,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I53">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J53">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2024-19</t>
+          <t>2019-42</t>
         </is>
       </c>
       <c r="L53" s="2">
-        <v>45139</v>
+        <v>43754</v>
       </c>
       <c r="M53" s="3">
-        <v>45420</v>
+        <v>43753</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -5232,16 +5232,16 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>18613513</v>
+        <v>17888898</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GUENTELICAN</t>
+          <t>NIETO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JUAN ANDRES</t>
+          <t>RAUL ENRIQUE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5270,21 +5270,21 @@
         </is>
       </c>
       <c r="I54">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="J54">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2025-33</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="L54" s="2">
-        <v>45883</v>
+        <v>44972</v>
       </c>
       <c r="M54" s="3">
-        <v>45883</v>
+        <v>44963</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -5318,12 +5318,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Tto en curso</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5339,16 +5339,16 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>27112019</v>
+        <v>27519553</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SELVA BEATRIZ</t>
+          <t>PATRICIA MARGARITA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5373,25 +5373,25 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>06. Caso DESCARTADO de Infección por VHC</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I55">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J55">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="L55" s="2">
-        <v>45363</v>
+        <v>45065</v>
       </c>
       <c r="M55" s="3">
-        <v>45348</v>
+        <v>45000</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -5411,16 +5411,16 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>24580401</v>
+        <v>93633114</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>PEREIRA PEREIRA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GRACIELA</t>
+          <t>JOSE ROBINSON</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5445,25 +5445,25 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I56">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J56">
         <v>2023</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2023-25</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="L56" s="2">
-        <v>45119</v>
+        <v>45065</v>
       </c>
       <c r="M56" s="3">
-        <v>45098</v>
+        <v>44959</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -5472,42 +5472,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -5518,26 +5483,26 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>32473179</v>
+        <v>25116055</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TOBAR GUERRA</t>
+          <t>HOYOS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CRISTIAN ARTURO</t>
+          <t>FABIANA PATRICIA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5552,25 +5517,25 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>07. En estudio para Hepatitis C</t>
         </is>
       </c>
       <c r="I57">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="J57">
         <v>2023</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-44</t>
         </is>
       </c>
       <c r="L57" s="2">
-        <v>45240</v>
+        <v>45236</v>
       </c>
       <c r="M57" s="3">
-        <v>44971</v>
+        <v>45229</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5579,42 +5544,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>HIV</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5625,16 +5555,16 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>13744342</v>
+        <v>14135708</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>LAURA GLADYS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5644,7 +5574,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5659,25 +5589,25 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 3</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J58">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="L58" s="2">
-        <v>44599</v>
+        <v>44178</v>
       </c>
       <c r="M58" s="3">
-        <v>44595</v>
+        <v>43902</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5691,7 +5621,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5721,37 +5651,37 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>31615481</v>
+        <v>14423827</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CANCINO</t>
+          <t>CANTERO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SILVANA NATALIA</t>
+          <t>LUIS ALBERTO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5766,29 +5696,29 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I59">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J59">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2023-15</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="L59" s="2">
-        <v>45065</v>
+        <v>43865</v>
       </c>
       <c r="M59" s="3">
-        <v>45027</v>
+        <v>43865</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5803,62 +5733,62 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>27541551</v>
+        <v>21816819</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DURAN</t>
+          <t>BARRIENTOS VIDAL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MARIA VANESA</t>
+          <t>LUIS GUILLERMO</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5873,69 +5803,34 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I60">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J60">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2023-40</t>
         </is>
       </c>
       <c r="L60" s="2">
-        <v>44628</v>
+        <v>45247</v>
       </c>
       <c r="M60" s="3">
-        <v>44628</v>
+        <v>45204</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>RIO TERCERO</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
           <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -5946,26 +5841,26 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>30566224</v>
+        <v>22668469</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SILVANA BEATRIZ</t>
+          <t>JULIO ARNALDO PABLO</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5984,25 +5879,25 @@
         </is>
       </c>
       <c r="I61">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="J61">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2024-21</t>
+          <t>2023-44</t>
         </is>
       </c>
       <c r="L61" s="2">
-        <v>45432</v>
+        <v>45236</v>
       </c>
       <c r="M61" s="3">
-        <v>45432</v>
+        <v>45233</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6012,62 +5907,62 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>22213030</v>
+        <v>34375222</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>MANCILLA MENDEZ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NESTOR DAVID</t>
+          <t>JORGE DAMIAN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6082,30 +5977,30 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>01. Caso probable en banco de sangre</t>
         </is>
       </c>
       <c r="I62">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J62">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2019-46</t>
+          <t>2025-49</t>
         </is>
       </c>
       <c r="L62" s="2">
-        <v>43803</v>
+        <v>46010</v>
       </c>
       <c r="M62" s="3">
-        <v>43780</v>
+        <v>45996</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -6114,42 +6009,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
           <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -6160,16 +6020,16 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>16711304</v>
+        <v>17438241</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ACETO</t>
+          <t>SANTILLAN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SANDRA ELISABET</t>
+          <t>HECTOR EDUARDO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6179,7 +6039,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6194,29 +6054,29 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 2</t>
+          <t>Virus Hepatitis C, genotipo 1</t>
         </is>
       </c>
       <c r="I63">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J63">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2020-29</t>
+          <t>2019-31</t>
         </is>
       </c>
       <c r="L63" s="2">
-        <v>44178</v>
+        <v>43690</v>
       </c>
       <c r="M63" s="3">
-        <v>44025</v>
+        <v>43679</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6267,16 +6127,16 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>23611807</v>
+        <v>25006616</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NAPOLEONE</t>
+          <t>PANIAGUA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SILVANA JAQUELINA</t>
+          <t>PAOLA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6301,25 +6161,25 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I64">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="J64">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2023-43</t>
+          <t>2022-32</t>
         </is>
       </c>
       <c r="L64" s="2">
-        <v>45236</v>
+        <v>44932</v>
       </c>
       <c r="M64" s="3">
-        <v>45225</v>
+        <v>44781</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -6338,7 +6198,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6358,7 +6218,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6374,16 +6234,16 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>22355486</v>
+        <v>20066627</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ACERBI</t>
+          <t>MASI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RAUL EDUARDO</t>
+          <t>CLAUDIA ESTER</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6393,7 +6253,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6408,29 +6268,29 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>06. Caso DESCARTADO de Infección por VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I65">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J65">
         <v>2019</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-13</t>
         </is>
       </c>
       <c r="L65" s="2">
-        <v>43627</v>
+        <v>44923</v>
       </c>
       <c r="M65" s="3">
-        <v>43493</v>
+        <v>43550</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6446,16 +6306,16 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>5159683</v>
+        <v>93744318</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t>AGUILA AGUILA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MARIA MIRTA</t>
+          <t>MIRNA ADELITA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6480,29 +6340,29 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I66">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="J66">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2022-18</t>
+          <t>2025-50</t>
         </is>
       </c>
       <c r="L66" s="2">
-        <v>44712</v>
+        <v>46041</v>
       </c>
       <c r="M66" s="3">
-        <v>44686</v>
+        <v>46000</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6517,7 +6377,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Tto en curso</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6532,17 +6392,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Tto en curso</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -6553,26 +6413,26 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>12000042</v>
+        <v>13844552</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BUSTOS</t>
+          <t>OVANDO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ERNESTO REYES</t>
+          <t>ROSA ESTHER</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6591,25 +6451,25 @@
         </is>
       </c>
       <c r="I67">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="J67">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2022-32</t>
         </is>
       </c>
       <c r="L67" s="2">
-        <v>45712</v>
+        <v>44833</v>
       </c>
       <c r="M67" s="3">
-        <v>45705</v>
+        <v>44782</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6624,7 +6484,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6639,12 +6499,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6660,16 +6520,16 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>94509088</v>
+        <v>94574916</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YECGUANCHUY CHAVEZ</t>
+          <t>ROA RESQUIN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RAUL ANTONY</t>
+          <t>NORMA ELIZABETH</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6679,7 +6539,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6694,69 +6554,34 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>05. Infección resuelta o falso anti VHC</t>
         </is>
       </c>
       <c r="I68">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J68">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2023-16</t>
+          <t>2024-32</t>
         </is>
       </c>
       <c r="L68" s="2">
-        <v>45246</v>
+        <v>45512</v>
       </c>
       <c r="M68" s="3">
-        <v>45034</v>
+        <v>45512</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>HIV</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -6767,16 +6592,16 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>13964678</v>
+        <v>20853965</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>BRUNO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JORGE DANIEL</t>
+          <t>MARCELO FABIAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6796,30 +6621,30 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>06. Caso DESCARTADO de Infección por VHC</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I69">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="J69">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2020-14</t>
+          <t>2019-38</t>
         </is>
       </c>
       <c r="L69" s="2">
-        <v>44082</v>
+        <v>43754</v>
       </c>
       <c r="M69" s="3">
-        <v>43922</v>
+        <v>43724</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -6828,7 +6653,42 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -6839,21 +6699,21 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>27817021</v>
+        <v>18265819</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ADRIANA MARISA</t>
+          <t>MARTA GLADYS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6873,29 +6733,29 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I70">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J70">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2023-21</t>
+          <t>2025-14</t>
         </is>
       </c>
       <c r="L70" s="2">
-        <v>45240</v>
+        <v>45748</v>
       </c>
       <c r="M70" s="3">
-        <v>45068</v>
+        <v>45748</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6910,7 +6770,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6930,7 +6790,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6946,16 +6806,16 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>14857249</v>
+        <v>21970773</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZALAZAR</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO</t>
+          <t>ROSA RAQUEL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6965,7 +6825,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6980,25 +6840,25 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 3</t>
+          <t>06. Caso DESCARTADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I71">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="J71">
         <v>2025</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-35</t>
         </is>
       </c>
       <c r="L71" s="2">
-        <v>45707</v>
+        <v>45898</v>
       </c>
       <c r="M71" s="3">
-        <v>45707</v>
+        <v>45897</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -7007,42 +6867,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -7053,21 +6878,21 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>13986860</v>
+        <v>33845183</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OSCAR JOSE</t>
+          <t>SERGIO ORLANDO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mayores de 65 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7087,29 +6912,29 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 4</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I72">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J72">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-16</t>
         </is>
       </c>
       <c r="L72" s="2">
-        <v>45498</v>
+        <v>45240</v>
       </c>
       <c r="M72" s="3">
-        <v>45348</v>
+        <v>45033</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7119,67 +6944,67 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>24880822</v>
+        <v>34423562</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>GASC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MONICA ANDREA</t>
+          <t>MARIO LEONARDO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>De 25 a 34 años</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7189,74 +7014,39 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I73">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="J73">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2018-45</t>
+          <t>2020-29</t>
         </is>
       </c>
       <c r="L73" s="2">
-        <v>43468</v>
+        <v>44176</v>
       </c>
       <c r="M73" s="3">
-        <v>43413</v>
+        <v>44027</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>TOLHUIN</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
           <t>SIN DATOS</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -7267,16 +7057,16 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>18084570</v>
+        <v>23851558</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PELAYES</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO</t>
+          <t>ANTONIO AUGUSTO</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7301,29 +7091,29 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I74">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J74">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2020-22</t>
+          <t>2023-15</t>
         </is>
       </c>
       <c r="L74" s="2">
-        <v>44178</v>
+        <v>45239</v>
       </c>
       <c r="M74" s="3">
-        <v>43980</v>
+        <v>45026</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7338,7 +7128,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7348,52 +7138,52 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>13326219</v>
+        <v>5123419</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>URRUTIA</t>
+          <t>ALBORNOZ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MIGUEL ESTEBAN</t>
+          <t>JUANA EUSEBIA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7408,29 +7198,29 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I75">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="J75">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2019-42</t>
+          <t>2024-22</t>
         </is>
       </c>
       <c r="L75" s="2">
-        <v>43754</v>
+        <v>45498</v>
       </c>
       <c r="M75" s="3">
-        <v>43753</v>
+        <v>45440</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7445,52 +7235,52 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>92825549</v>
+        <v>20897254</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NAIPIL BUSTOS</t>
+          <t>MANSILLA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ALEJANDRO VLADIMIR</t>
+          <t>SILVIA ALEJANDRA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7500,7 +7290,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7519,25 +7309,25 @@
         </is>
       </c>
       <c r="I76">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="J76">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2020-41</t>
+          <t>2024-19</t>
         </is>
       </c>
       <c r="L76" s="2">
-        <v>44178</v>
+        <v>45139</v>
       </c>
       <c r="M76" s="3">
-        <v>44109</v>
+        <v>45420</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7547,7 +7337,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -7572,12 +7362,12 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -7588,16 +7378,16 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>17888898</v>
+        <v>18613513</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NIETO</t>
+          <t>GUENTELICAN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>RAUL ENRIQUE</t>
+          <t>JUAN ANDRES</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7626,21 +7416,21 @@
         </is>
       </c>
       <c r="I77">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="J77">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2025-33</t>
         </is>
       </c>
       <c r="L77" s="2">
-        <v>44972</v>
+        <v>45883</v>
       </c>
       <c r="M77" s="3">
-        <v>44963</v>
+        <v>45883</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -7674,12 +7464,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Tto en curso</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7695,16 +7485,16 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>14423827</v>
+        <v>24580401</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CANTERO</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>GRACIELA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7714,7 +7504,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7729,29 +7519,29 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>04. Caso CONFIRMADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I78">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J78">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2023-25</t>
         </is>
       </c>
       <c r="L78" s="2">
-        <v>43865</v>
+        <v>45119</v>
       </c>
       <c r="M78" s="3">
-        <v>43865</v>
+        <v>45098</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>*SIN DATO* (*SIN DATO*)</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7766,7 +7556,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7776,17 +7566,17 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7796,27 +7586,27 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>14135708</v>
+        <v>27112019</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LAURA GLADYS</t>
+          <t>SELVA BEATRIZ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7836,25 +7626,25 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>06. Caso DESCARTADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I79">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J79">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="L79" s="2">
-        <v>44178</v>
+        <v>45363</v>
       </c>
       <c r="M79" s="3">
-        <v>43902</v>
+        <v>45348</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -7863,67 +7653,32 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>93633114</v>
+        <v>10691387</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PEREIRA PEREIRA</t>
+          <t>MORUA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JOSE ROBINSON</t>
+          <t>VICTOR HUGO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7943,34 +7698,69 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 3</t>
         </is>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="J80">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2025-27</t>
         </is>
       </c>
       <c r="L80" s="2">
-        <v>45065</v>
+        <v>45840</v>
       </c>
       <c r="M80" s="3">
-        <v>44959</v>
+        <v>45838</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Tto en curso</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -7981,26 +7771,26 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>21816819</v>
+        <v>31615481</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BARRIENTOS VIDAL</t>
+          <t>CANCINO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LUIS GUILLERMO</t>
+          <t>SILVANA NATALIA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -8015,25 +7805,25 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1</t>
         </is>
       </c>
       <c r="I81">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="J81">
         <v>2023</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2023-40</t>
+          <t>2023-15</t>
         </is>
       </c>
       <c r="L81" s="2">
-        <v>45247</v>
+        <v>45065</v>
       </c>
       <c r="M81" s="3">
-        <v>45204</v>
+        <v>45027</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -8042,7 +7832,42 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
           <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -8053,16 +7878,16 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>27519553</v>
+        <v>27541551</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>DURAN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PATRICIA MARGARITA</t>
+          <t>MARIA VANESA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -8087,34 +7912,69 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I82">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J82">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="L82" s="2">
-        <v>45065</v>
+        <v>44628</v>
       </c>
       <c r="M82" s="3">
-        <v>45000</v>
+        <v>44628</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>RIO TERCERO</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
           <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -8125,16 +7985,16 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>25116055</v>
+        <v>13744342</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HOYOS</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FABIANA PATRICIA</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -8144,7 +8004,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -8159,25 +8019,25 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>07. En estudio para Hepatitis C</t>
+          <t>Virus Hepatitis C, genotipo 3</t>
         </is>
       </c>
       <c r="I83">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="J83">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2023-44</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="L83" s="2">
-        <v>45236</v>
+        <v>44599</v>
       </c>
       <c r="M83" s="3">
-        <v>45229</v>
+        <v>44595</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -8186,7 +8046,42 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -8197,16 +8092,16 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>34375222</v>
+        <v>32473179</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MANCILLA MENDEZ</t>
+          <t>TOBAR GUERRA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JORGE DAMIAN</t>
+          <t>CRISTIAN ARTURO</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -8226,30 +8121,30 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Banco de Sangre</t>
+          <t>Hepatitis virales</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01. Caso probable en banco de sangre</t>
+          <t>Virus Hepatitis C, genotipo 1a</t>
         </is>
       </c>
       <c r="I84">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="J84">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2025-49</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="L84" s="2">
-        <v>46010</v>
+        <v>45240</v>
       </c>
       <c r="M84" s="3">
-        <v>45996</v>
+        <v>44971</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -8258,7 +8153,42 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>HIV</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -8269,26 +8199,26 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>22668469</v>
+        <v>30566224</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JULIO ARNALDO PABLO</t>
+          <t>SILVANA BEATRIZ</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8307,25 +8237,25 @@
         </is>
       </c>
       <c r="I85">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="J85">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2023-44</t>
+          <t>2024-21</t>
         </is>
       </c>
       <c r="L85" s="2">
-        <v>45236</v>
+        <v>45432</v>
       </c>
       <c r="M85" s="3">
-        <v>45233</v>
+        <v>45432</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8335,57 +8265,57 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>17438241</v>
+        <v>23611807</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SANTILLAN</t>
+          <t>NAPOLEONE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HECTOR EDUARDO</t>
+          <t>SILVANA JAQUELINA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -8395,7 +8325,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8414,21 +8344,21 @@
         </is>
       </c>
       <c r="I86">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="J86">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2019-31</t>
+          <t>2023-43</t>
         </is>
       </c>
       <c r="L86" s="2">
-        <v>43690</v>
+        <v>45236</v>
       </c>
       <c r="M86" s="3">
-        <v>43679</v>
+        <v>45225</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -8462,7 +8392,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -8472,7 +8402,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
@@ -8483,16 +8413,16 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>20066627</v>
+        <v>16711304</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MASI</t>
+          <t>ACETO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CLAUDIA ESTER</t>
+          <t>SANDRA ELISABET</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -8517,34 +8447,69 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 2</t>
         </is>
       </c>
       <c r="I87">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J87">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2019-13</t>
+          <t>2020-29</t>
         </is>
       </c>
       <c r="L87" s="2">
-        <v>44923</v>
+        <v>44178</v>
       </c>
       <c r="M87" s="3">
-        <v>43550</v>
+        <v>44025</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -8555,16 +8520,16 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>25006616</v>
+        <v>22213030</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PANIAGUA</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PAOLA</t>
+          <t>NESTOR DAVID</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8574,7 +8539,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -8593,21 +8558,21 @@
         </is>
       </c>
       <c r="I88">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="J88">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2022-32</t>
+          <t>2019-46</t>
         </is>
       </c>
       <c r="L88" s="2">
-        <v>44932</v>
+        <v>43803</v>
       </c>
       <c r="M88" s="3">
-        <v>44781</v>
+        <v>43780</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -8626,7 +8591,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8641,12 +8606,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8662,16 +8627,16 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>13844552</v>
+        <v>22355486</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OVANDO</t>
+          <t>ACERBI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ROSA ESTHER</t>
+          <t>RAUL EDUARDO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8681,7 +8646,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -8696,69 +8661,34 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1b</t>
+          <t>06. Caso DESCARTADO de Infección por VHC</t>
         </is>
       </c>
       <c r="I89">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="J89">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2022-32</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="L89" s="2">
-        <v>44833</v>
+        <v>43627</v>
       </c>
       <c r="M89" s="3">
-        <v>44782</v>
+        <v>43493</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -8769,16 +8699,16 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>93744318</v>
+        <v>5159683</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AGUILA AGUILA</t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MIRNA ADELITA</t>
+          <t>MARIA MIRTA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8803,29 +8733,29 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Virus Hepatitis C, genotipo 1a</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I90">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="J90">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2025-50</t>
+          <t>2022-18</t>
         </is>
       </c>
       <c r="L90" s="2">
-        <v>46041</v>
+        <v>44712</v>
       </c>
       <c r="M90" s="3">
-        <v>46000</v>
+        <v>44686</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8840,7 +8770,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Tto en curso</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8855,17 +8785,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>Tto en curso</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -8876,26 +8806,26 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>94574916</v>
+        <v>12000042</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ROA RESQUIN</t>
+          <t>BUSTOS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NORMA ELIZABETH</t>
+          <t>ERNESTO REYES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>De 35 a 44 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -8910,34 +8840,69 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>05. Infección resuelta o falso anti VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I91">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J91">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2024-32</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="L91" s="2">
-        <v>45512</v>
+        <v>45712</v>
       </c>
       <c r="M91" s="3">
-        <v>45512</v>
+        <v>45705</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>*SIN DATO* (*SIN DATO*)</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -8948,26 +8913,26 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>18265819</v>
+        <v>94509088</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>YECGUANCHUY CHAVEZ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MARTA GLADYS</t>
+          <t>RAUL ANTONY</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8986,25 +8951,25 @@
         </is>
       </c>
       <c r="I92">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J92">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2025-14</t>
+          <t>2023-16</t>
         </is>
       </c>
       <c r="L92" s="2">
-        <v>45748</v>
+        <v>45246</v>
       </c>
       <c r="M92" s="3">
-        <v>45748</v>
+        <v>45034</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>RIO GRANDE</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -9014,12 +8979,12 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -9039,12 +9004,12 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SIN DATOS</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -9055,16 +9020,16 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>21970773</v>
+        <v>13964678</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ROSA RAQUEL</t>
+          <t>JORGE DANIEL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9074,7 +9039,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -9084,7 +9049,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatitis virales</t>
+          <t>Banco de Sangre</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9093,21 +9058,21 @@
         </is>
       </c>
       <c r="I93">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="J93">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2025-35</t>
+          <t>2020-14</t>
         </is>
       </c>
       <c r="L93" s="2">
-        <v>45898</v>
+        <v>44082</v>
       </c>
       <c r="M93" s="3">
-        <v>45897</v>
+        <v>43922</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -9127,16 +9092,16 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>20853965</v>
+        <v>14857249</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BRUNO</t>
+          <t>ZALAZAR</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -9161,25 +9126,25 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 3</t>
         </is>
       </c>
       <c r="I94">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J94">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2019-38</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="L94" s="2">
-        <v>43754</v>
+        <v>45707</v>
       </c>
       <c r="M94" s="3">
-        <v>43724</v>
+        <v>45707</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -9223,7 +9188,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
@@ -9234,26 +9199,26 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>12693857</v>
+        <v>13986860</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OLGA BEATRIZ</t>
+          <t>OSCAR JOSE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>De 45 a 65 años</t>
+          <t>Mayores de 65 años</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -9268,25 +9233,25 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 4</t>
         </is>
       </c>
       <c r="I95">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="J95">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2018-52</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="L95" s="2">
-        <v>43503</v>
+        <v>45498</v>
       </c>
       <c r="M95" s="3">
-        <v>43461</v>
+        <v>45348</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -9295,37 +9260,72 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>DESCARTADO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SIN DATOS</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>34423562</v>
+        <v>27817021</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GASC</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MARIO LEONARDO</t>
+          <t>ADRIANA MARISA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 35 a 44 años</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -9340,34 +9340,69 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>03. Caso PROBABLE de Infección por VHC</t>
+          <t>Virus Hepatitis C, genotipo 1b</t>
         </is>
       </c>
       <c r="I96">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J96">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2020-29</t>
+          <t>2023-21</t>
         </is>
       </c>
       <c r="L96" s="2">
-        <v>44176</v>
+        <v>45240</v>
       </c>
       <c r="M96" s="3">
-        <v>44027</v>
+        <v>45068</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>TOLHUIN</t>
+          <t>USHUAIA</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>SIN DATOS</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
@@ -9557,26 +9592,26 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>33845183</v>
+        <v>12693857</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SERGIO ORLANDO</t>
+          <t>OLGA BEATRIZ</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>De 25 a 34 años</t>
+          <t>De 45 a 65 años</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -9591,69 +9626,34 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>04. Caso CONFIRMADO de Infección por VHC</t>
+          <t>03. Caso PROBABLE de Infección por VHC</t>
         </is>
       </c>
       <c r="I99">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="J99">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2023-16</t>
+          <t>2018-52</t>
         </is>
       </c>
       <c r="L99" s="2">
-        <v>45240</v>
+        <v>43503</v>
       </c>
       <c r="M99" s="3">
-        <v>45033</v>
+        <v>43461</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>USHUAIA</t>
+          <t>RIO GRANDE</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>HIV</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>DESCARTADO</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
